--- a/public/exports/Analisis_Cafe_Combo_RM.xlsx
+++ b/public/exports/Analisis_Cafe_Combo_RM.xlsx
@@ -475,7 +475,7 @@
         <v>VAN base</v>
       </c>
       <c r="B11" s="1">
-        <v>47193532</v>
+        <v>48686717</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +483,7 @@
         <v>TIR base</v>
       </c>
       <c r="B12" s="2">
-        <v>0.3847445262871899</v>
+        <v>0.3897448098295899</v>
       </c>
     </row>
     <row r="13">
@@ -1231,7 +1231,7 @@
         <v>VAN base</v>
       </c>
       <c r="B6" t="str">
-        <v>$47.193.532</v>
+        <v>$48.686.717</v>
       </c>
     </row>
     <row r="7">
@@ -1239,7 +1239,7 @@
         <v>TIR</v>
       </c>
       <c r="B7" t="str">
-        <v>38.5%</v>
+        <v>39.0%</v>
       </c>
     </row>
     <row r="8">
@@ -1315,10 +1315,10 @@
         <v>El Golf · Las Condes</v>
       </c>
       <c r="B21" t="str">
-        <v>$47.193.532</v>
+        <v>$48.686.717</v>
       </c>
       <c r="C21" t="str">
-        <v>38.5%</v>
+        <v>39.0%</v>
       </c>
       <c r="D21" t="str">
         <v>Score 65</v>
@@ -1334,13 +1334,13 @@
         <v>Santiago Centro · Ahumada</v>
       </c>
       <c r="B24" t="str">
-        <v>$2.077.091</v>
+        <v>$3.570.276</v>
       </c>
       <c r="C24" t="str">
-        <v>15.3%</v>
+        <v>16.1%</v>
       </c>
       <c r="D24" t="str">
-        <v>Score 52</v>
+        <v>Score 53</v>
       </c>
     </row>
     <row r="25">
@@ -1348,13 +1348,13 @@
         <v>Providencia · Pedro de Valdivia</v>
       </c>
       <c r="B25" t="str">
-        <v>$924.515</v>
+        <v>$2.417.700</v>
       </c>
       <c r="C25" t="str">
-        <v>14.6%</v>
+        <v>15.5%</v>
       </c>
       <c r="D25" t="str">
-        <v>Score 50</v>
+        <v>Score 51</v>
       </c>
     </row>
     <row r="26">
@@ -1362,13 +1362,13 @@
         <v>Apoquindo / El Bosque · Las Condes</v>
       </c>
       <c r="B26" t="str">
-        <v>$-16.380.285</v>
+        <v>$-14.887.101</v>
       </c>
       <c r="C26" t="str">
-        <v>3.0%</v>
+        <v>4.3%</v>
       </c>
       <c r="D26" t="str">
-        <v>Score 35</v>
+        <v>Score 37</v>
       </c>
     </row>
     <row r="27">
@@ -1376,13 +1376,13 @@
         <v>Estación Central · USACH</v>
       </c>
       <c r="B27" t="str">
-        <v>$-48.829.832</v>
+        <v>$-47.336.647</v>
       </c>
       <c r="C27" t="str">
         <v>—</v>
       </c>
       <c r="D27" t="str">
-        <v>Score 4</v>
+        <v>Score 5</v>
       </c>
     </row>
     <row r="28">
@@ -1390,7 +1390,7 @@
         <v>Vitacura · Alonso de Córdova</v>
       </c>
       <c r="B28" t="str">
-        <v>$-57.733.984</v>
+        <v>$-56.240.799</v>
       </c>
       <c r="C28" t="str">
         <v>—</v>
@@ -1404,7 +1404,7 @@
         <v>Ñuñoa · Plaza Ñuñoa</v>
       </c>
       <c r="B29" t="str">
-        <v>$-64.747.767</v>
+        <v>$-63.254.582</v>
       </c>
       <c r="C29" t="str">
         <v>—</v>
@@ -3727,16 +3727,16 @@
         <v>14207499</v>
       </c>
       <c r="G2" s="1">
-        <v>47193532</v>
+        <v>48686717</v>
       </c>
       <c r="H2" s="1">
-        <v>-86576396</v>
+        <v>-85083211</v>
       </c>
       <c r="I2" s="1">
-        <v>167809266</v>
+        <v>169302451</v>
       </c>
       <c r="J2" s="2">
-        <v>0.3847445262871899</v>
+        <v>0.3897448098295899</v>
       </c>
       <c r="K2">
         <v>3.39</v>
@@ -3768,22 +3768,22 @@
         <v>3904167</v>
       </c>
       <c r="G3" s="1">
-        <v>2077091</v>
+        <v>3570276</v>
       </c>
       <c r="H3" s="1">
-        <v>-109033202</v>
+        <v>-107540017</v>
       </c>
       <c r="I3" s="1">
-        <v>133672799</v>
+        <v>135165983</v>
       </c>
       <c r="J3" s="2">
-        <v>0.1526834996817253</v>
+        <v>0.16143628907794347</v>
       </c>
       <c r="K3">
-        <v>4.38</v>
+        <v>4.36</v>
       </c>
       <c r="L3">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M3" t="str">
         <v>No conviene</v>
@@ -3809,22 +3809,22 @@
         <v>3264435</v>
       </c>
       <c r="G4" s="1">
-        <v>924515</v>
+        <v>2417700</v>
       </c>
       <c r="H4" s="1">
-        <v>-111000697</v>
+        <v>-109507512</v>
       </c>
       <c r="I4" s="1">
-        <v>122269175</v>
+        <v>123762360</v>
       </c>
       <c r="J4" s="2">
-        <v>0.14584911340708784</v>
+        <v>0.15502872448589966</v>
       </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="L4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M4" t="str">
         <v>No conviene</v>
@@ -3850,22 +3850,22 @@
         <v>-819573</v>
       </c>
       <c r="G5" s="1">
-        <v>-16380285</v>
+        <v>-14887101</v>
       </c>
       <c r="H5" s="1">
-        <v>-133851616</v>
+        <v>-132358431</v>
       </c>
       <c r="I5" s="1">
-        <v>94492484</v>
+        <v>95985669</v>
       </c>
       <c r="J5" s="2">
-        <v>0.030419458943885074</v>
+        <v>0.04255006204542362</v>
       </c>
       <c r="K5">
-        <v>4.85</v>
+        <v>4.79</v>
       </c>
       <c r="L5">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M5" t="str">
         <v>No conviene</v>
@@ -3891,19 +3891,19 @@
         <v>-6839553</v>
       </c>
       <c r="G6" s="1">
-        <v>-48829832</v>
+        <v>-47336647</v>
       </c>
       <c r="H6" s="1">
-        <v>-151978474</v>
+        <v>-150485289</v>
       </c>
       <c r="I6" s="1">
-        <v>75980216</v>
+        <v>77473401</v>
       </c>
       <c r="K6" t="str">
         <v>&gt; 5</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6" t="str">
         <v>No conviene</v>
@@ -3929,13 +3929,13 @@
         <v>-9137745</v>
       </c>
       <c r="G7" s="1">
-        <v>-57733984</v>
+        <v>-56240799</v>
       </c>
       <c r="H7" s="1">
-        <v>-172091276</v>
+        <v>-170598091</v>
       </c>
       <c r="I7" s="1">
-        <v>59882646</v>
+        <v>61375831</v>
       </c>
       <c r="K7" t="str">
         <v>&gt; 5</v>
@@ -3967,13 +3967,13 @@
         <v>-10274865</v>
       </c>
       <c r="G8" s="1">
-        <v>-64747767</v>
+        <v>-63254582</v>
       </c>
       <c r="H8" s="1">
-        <v>-149567682</v>
+        <v>-148074497</v>
       </c>
       <c r="I8" s="1">
-        <v>37415708</v>
+        <v>38908893</v>
       </c>
       <c r="K8" t="str">
         <v>&gt; 5</v>
@@ -4012,7 +4012,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>VAN 47.193.532  ·  TIR 38.5%  ·  Payback 3.39 años</v>
+        <v>VAN 48.686.717  ·  TIR 39.0%  ·  Payback 3.39 años</v>
       </c>
     </row>
     <row r="4">
@@ -4357,7 +4357,7 @@
         <v/>
       </c>
       <c r="G18" s="1">
-        <v>1537500</v>
+        <v>4412500</v>
       </c>
     </row>
     <row r="19">
@@ -4449,7 +4449,7 @@
         <v>15866859.94328748</v>
       </c>
       <c r="G22" s="1">
-        <v>101947269.72775845</v>
+        <v>104822269.72775845</v>
       </c>
     </row>
     <row r="24">
@@ -4462,7 +4462,7 @@
         <v>VAN</v>
       </c>
       <c r="B25" s="1">
-        <v>47193532</v>
+        <v>48686717</v>
       </c>
     </row>
     <row r="26">
@@ -4470,7 +4470,7 @@
         <v>TIR</v>
       </c>
       <c r="B26" s="2">
-        <v>0.3847445262871899</v>
+        <v>0.3897448098295899</v>
       </c>
     </row>
     <row r="27">
@@ -4531,7 +4531,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>VAN base: $47.193.532</v>
+        <v>VAN base: $48.686.717</v>
       </c>
     </row>
     <row r="4">
@@ -4559,19 +4559,19 @@
         <v>Ticket promedio</v>
       </c>
       <c r="B5" s="1">
-        <v>-71783171</v>
+        <v>-70289986</v>
       </c>
       <c r="C5" s="1">
-        <v>-7242653</v>
+        <v>-5749468</v>
       </c>
       <c r="D5" s="1">
-        <v>47193532</v>
+        <v>48686717</v>
       </c>
       <c r="E5" s="1">
-        <v>101570988</v>
+        <v>103064172</v>
       </c>
       <c r="F5" s="1">
-        <v>155948443</v>
+        <v>157441628</v>
       </c>
     </row>
     <row r="6">
@@ -4579,19 +4579,19 @@
         <v>Demanda (combos/día)</v>
       </c>
       <c r="B6" s="1">
-        <v>-19470979</v>
+        <v>-17977794</v>
       </c>
       <c r="C6" s="1">
-        <v>14454976</v>
+        <v>15948161</v>
       </c>
       <c r="D6" s="1">
-        <v>47193532</v>
+        <v>48686717</v>
       </c>
       <c r="E6" s="1">
-        <v>79932089</v>
+        <v>81425274</v>
       </c>
       <c r="F6" s="1">
-        <v>112670645</v>
+        <v>114163830</v>
       </c>
     </row>
     <row r="7">
@@ -4599,19 +4599,19 @@
         <v>Costo variable insumo</v>
       </c>
       <c r="B7" s="1">
-        <v>90471330</v>
+        <v>91964515</v>
       </c>
       <c r="C7" s="1">
-        <v>68832431</v>
+        <v>70325616</v>
       </c>
       <c r="D7" s="1">
-        <v>47193532</v>
+        <v>48686717</v>
       </c>
       <c r="E7" s="1">
-        <v>25554633</v>
+        <v>27047818</v>
       </c>
       <c r="F7" s="1">
-        <v>3915734</v>
+        <v>5408919</v>
       </c>
     </row>
     <row r="8">
@@ -4619,19 +4619,19 @@
         <v>Arriendo UF/m²</v>
       </c>
       <c r="B8" s="1">
-        <v>59922610</v>
+        <v>61415795</v>
       </c>
       <c r="C8" s="1">
-        <v>53558071</v>
+        <v>55051256</v>
       </c>
       <c r="D8" s="1">
-        <v>47193532</v>
+        <v>48686717</v>
       </c>
       <c r="E8" s="1">
-        <v>40828993</v>
+        <v>42322178</v>
       </c>
       <c r="F8" s="1">
-        <v>34464454</v>
+        <v>35957639</v>
       </c>
     </row>
     <row r="9">
@@ -4639,19 +4639,19 @@
         <v>Sueldos planilla</v>
       </c>
       <c r="B9" s="1">
-        <v>65376516</v>
+        <v>66869701</v>
       </c>
       <c r="C9" s="1">
-        <v>56285024</v>
+        <v>57778209</v>
       </c>
       <c r="D9" s="1">
-        <v>47193532</v>
+        <v>48686717</v>
       </c>
       <c r="E9" s="1">
-        <v>38102040</v>
+        <v>39595225</v>
       </c>
       <c r="F9" s="1">
-        <v>29010548</v>
+        <v>30503733</v>
       </c>
     </row>
     <row r="11">
@@ -4693,7 +4693,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>54377456</v>
+        <v>54377455</v>
       </c>
       <c r="F13" s="1">
         <v>108754911</v>

--- a/public/exports/Analisis_Cafe_Combo_RM.xlsx
+++ b/public/exports/Analisis_Cafe_Combo_RM.xlsx
@@ -475,7 +475,7 @@
         <v>VAN base</v>
       </c>
       <c r="B11" s="1">
-        <v>48686717</v>
+        <v>161650312</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +483,7 @@
         <v>TIR base</v>
       </c>
       <c r="B12" s="2">
-        <v>0.3897448098295899</v>
+        <v>0.6245770437265755</v>
       </c>
     </row>
     <row r="13">
@@ -491,7 +491,7 @@
         <v>Payback (años)</v>
       </c>
       <c r="B13">
-        <v>3.3885727033412385</v>
+        <v>2.572724307463795</v>
       </c>
     </row>
     <row r="14">
@@ -499,7 +499,7 @@
         <v>Inversión total</v>
       </c>
       <c r="B14" s="1">
-        <v>44549554</v>
+        <v>51069054</v>
       </c>
     </row>
     <row r="15">
@@ -507,7 +507,7 @@
         <v>EBITDA año 1</v>
       </c>
       <c r="B15" s="1">
-        <v>14207499</v>
+        <v>5614332</v>
       </c>
     </row>
     <row r="16">
@@ -515,7 +515,7 @@
         <v>Veredicto</v>
       </c>
       <c r="B16" t="str">
-        <v>Aceptable con riesgo</v>
+        <v>Recomendado</v>
       </c>
     </row>
     <row r="17">
@@ -523,7 +523,7 @@
         <v>Score de viabilidad (0-100)</v>
       </c>
       <c r="B17">
-        <v>65</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -1231,7 +1231,7 @@
         <v>VAN base</v>
       </c>
       <c r="B6" t="str">
-        <v>$48.686.717</v>
+        <v>$161.650.312</v>
       </c>
     </row>
     <row r="7">
@@ -1239,7 +1239,7 @@
         <v>TIR</v>
       </c>
       <c r="B7" t="str">
-        <v>39.0%</v>
+        <v>62.5%</v>
       </c>
     </row>
     <row r="8">
@@ -1247,7 +1247,7 @@
         <v>Payback</v>
       </c>
       <c r="B8" t="str">
-        <v>3.39 años</v>
+        <v>2.57 años</v>
       </c>
     </row>
     <row r="9">
@@ -1255,7 +1255,7 @@
         <v>Inversión inicial</v>
       </c>
       <c r="B9" t="str">
-        <v>$44.549.554</v>
+        <v>$51.069.054</v>
       </c>
     </row>
     <row r="10">
@@ -1263,7 +1263,7 @@
         <v>Combos/día base</v>
       </c>
       <c r="B10">
-        <v>95</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -1271,7 +1271,7 @@
         <v>EBITDA año 1</v>
       </c>
       <c r="B11" t="str">
-        <v>$14.207.499</v>
+        <v>$5.614.332</v>
       </c>
     </row>
     <row r="12">
@@ -1287,7 +1287,7 @@
         <v>Score viabilidad</v>
       </c>
       <c r="B13" t="str">
-        <v>65 / 100</v>
+        <v>100 / 100</v>
       </c>
     </row>
     <row r="15">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>✅ Recomendadas (1)</v>
+        <v>✅ Recomendadas (6)</v>
       </c>
     </row>
     <row r="21">
@@ -1315,18 +1315,41 @@
         <v>El Golf · Las Condes</v>
       </c>
       <c r="B21" t="str">
-        <v>$48.686.717</v>
+        <v>$161.650.312</v>
       </c>
       <c r="C21" t="str">
-        <v>39.0%</v>
+        <v>62.5%</v>
       </c>
       <c r="D21" t="str">
-        <v>Score 65</v>
+        <v>Score 100</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Providencia · Pedro de Valdivia</v>
+      </c>
+      <c r="B22" t="str">
+        <v>$154.338.627</v>
+      </c>
+      <c r="C22" t="str">
+        <v>61.7%</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Score 100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>❌ No recomendadas (6)</v>
+        <v>Apoquindo / El Bosque · Las Condes</v>
+      </c>
+      <c r="B23" t="str">
+        <v>$98.709.622</v>
+      </c>
+      <c r="C23" t="str">
+        <v>46.9%</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Score 65</v>
       </c>
     </row>
     <row r="24">
@@ -1334,83 +1357,60 @@
         <v>Santiago Centro · Ahumada</v>
       </c>
       <c r="B24" t="str">
-        <v>$3.570.276</v>
+        <v>$87.093.900</v>
       </c>
       <c r="C24" t="str">
-        <v>16.1%</v>
+        <v>43.3%</v>
       </c>
       <c r="D24" t="str">
-        <v>Score 53</v>
+        <v>Score 65</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Providencia · Pedro de Valdivia</v>
+        <v>Vitacura · Alonso de Córdova</v>
       </c>
       <c r="B25" t="str">
-        <v>$2.417.700</v>
+        <v>$46.270.049</v>
       </c>
       <c r="C25" t="str">
-        <v>15.5%</v>
+        <v>31.2%</v>
       </c>
       <c r="D25" t="str">
-        <v>Score 51</v>
+        <v>Score 65</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Apoquindo / El Bosque · Las Condes</v>
+        <v>Ñuñoa · Plaza Ñuñoa</v>
       </c>
       <c r="B26" t="str">
-        <v>$-14.887.101</v>
+        <v>$27.541.729</v>
       </c>
       <c r="C26" t="str">
-        <v>4.3%</v>
+        <v>25.2%</v>
       </c>
       <c r="D26" t="str">
-        <v>Score 37</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>Estación Central · USACH</v>
-      </c>
-      <c r="B27" t="str">
-        <v>$-47.336.647</v>
-      </c>
-      <c r="C27" t="str">
-        <v>—</v>
-      </c>
-      <c r="D27" t="str">
-        <v>Score 5</v>
+        <v>Score 65</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Vitacura · Alonso de Córdova</v>
-      </c>
-      <c r="B28" t="str">
-        <v>$-56.240.799</v>
-      </c>
-      <c r="C28" t="str">
-        <v>—</v>
-      </c>
-      <c r="D28" t="str">
-        <v>Score 0</v>
+        <v>❌ No recomendadas (1)</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Ñuñoa · Plaza Ñuñoa</v>
+        <v>Estación Central · USACH</v>
       </c>
       <c r="B29" t="str">
-        <v>$-63.254.582</v>
+        <v>$-23.503.844</v>
       </c>
       <c r="C29" t="str">
-        <v>—</v>
+        <v>3.0%</v>
       </c>
       <c r="D29" t="str">
-        <v>Score 0</v>
+        <v>Score 38</v>
       </c>
     </row>
     <row r="31">
@@ -2093,7 +2093,7 @@
         <v>0.6222222222222222</v>
       </c>
       <c r="R2" s="5">
-        <v>95</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3">
@@ -2101,55 +2101,55 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Santiago Centro · Ahumada</v>
+        <v>Providencia · Pedro de Valdivia</v>
       </c>
       <c r="C3" t="str">
-        <v>Santiago</v>
+        <v>Providencia</v>
       </c>
       <c r="D3" t="str">
-        <v>Paseo Ahumada / Estado</v>
+        <v>Pedro de Valdivia 1700 - 2400</v>
       </c>
       <c r="E3" s="4">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="F3" s="5">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G3" s="1">
-        <v>651750</v>
+        <v>898625</v>
       </c>
       <c r="H3" s="1">
-        <v>140000</v>
+        <v>150000</v>
       </c>
       <c r="I3" s="1">
-        <v>55000</v>
+        <v>65000</v>
       </c>
       <c r="J3" s="1">
-        <v>1696750</v>
+        <v>1963625</v>
       </c>
       <c r="K3" s="5">
-        <v>95000</v>
+        <v>38000</v>
       </c>
       <c r="L3" s="5">
-        <v>145</v>
+        <v>92</v>
       </c>
       <c r="M3" s="1">
-        <v>1380000</v>
+        <v>2980000</v>
       </c>
       <c r="N3" s="5">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="O3" s="1">
-        <v>2900</v>
+        <v>3700</v>
       </c>
       <c r="P3" s="1">
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.5344827586206896</v>
+        <v>0.5945945945945946</v>
       </c>
       <c r="R3" s="5">
-        <v>130</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4">
@@ -2157,55 +2157,55 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Providencia · Pedro de Valdivia</v>
+        <v>Apoquindo / El Bosque · Las Condes</v>
       </c>
       <c r="C4" t="str">
-        <v>Providencia</v>
+        <v>Las Condes</v>
       </c>
       <c r="D4" t="str">
-        <v>Pedro de Valdivia 1700 - 2400</v>
+        <v>Apoquindo 4000 - 4900</v>
       </c>
       <c r="E4" s="4">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="F4" s="5">
         <v>35</v>
       </c>
       <c r="G4" s="1">
-        <v>898625</v>
+        <v>1036875</v>
       </c>
       <c r="H4" s="1">
-        <v>150000</v>
+        <v>180000</v>
       </c>
       <c r="I4" s="1">
-        <v>65000</v>
+        <v>75000</v>
       </c>
       <c r="J4" s="1">
-        <v>1963625</v>
+        <v>2141875</v>
       </c>
       <c r="K4" s="5">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="L4" s="5">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="M4" s="1">
-        <v>2980000</v>
+        <v>3650000</v>
       </c>
       <c r="N4" s="5">
-        <v>95</v>
+        <v>220</v>
       </c>
       <c r="O4" s="1">
-        <v>3700</v>
+        <v>3800</v>
       </c>
       <c r="P4" s="1">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.5945945945945946</v>
+        <v>0.5921052631578947</v>
       </c>
       <c r="R4" s="5">
-        <v>95</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5">
@@ -2213,55 +2213,55 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Apoquindo / El Bosque · Las Condes</v>
+        <v>Santiago Centro · Ahumada</v>
       </c>
       <c r="C5" t="str">
-        <v>Las Condes</v>
+        <v>Santiago</v>
       </c>
       <c r="D5" t="str">
-        <v>Apoquindo 4000 - 4900</v>
+        <v>Paseo Ahumada / Estado</v>
       </c>
       <c r="E5" s="4">
-        <v>0.75</v>
+        <v>0.55</v>
       </c>
       <c r="F5" s="5">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G5" s="1">
-        <v>1036875</v>
+        <v>651750</v>
       </c>
       <c r="H5" s="1">
-        <v>180000</v>
+        <v>140000</v>
       </c>
       <c r="I5" s="1">
-        <v>75000</v>
+        <v>55000</v>
       </c>
       <c r="J5" s="1">
-        <v>2141875</v>
+        <v>1696750</v>
       </c>
       <c r="K5" s="5">
-        <v>35000</v>
+        <v>95000</v>
       </c>
       <c r="L5" s="5">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="M5" s="1">
-        <v>3650000</v>
+        <v>1380000</v>
       </c>
       <c r="N5" s="5">
-        <v>220</v>
+        <v>80</v>
       </c>
       <c r="O5" s="1">
-        <v>3800</v>
+        <v>2900</v>
       </c>
       <c r="P5" s="1">
-        <v>1550</v>
+        <v>1350</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.5921052631578947</v>
+        <v>0.5344827586206896</v>
       </c>
       <c r="R5" s="5">
-        <v>90</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6">
@@ -2269,55 +2269,55 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Estación Central · USACH</v>
+        <v>Vitacura · Alonso de Córdova</v>
       </c>
       <c r="C6" t="str">
-        <v>Estación Central</v>
+        <v>Vitacura</v>
       </c>
       <c r="D6" t="str">
-        <v>Av. Bdo OHiggins 3300 - 3700</v>
+        <v>Alonso de Córdova 3000 - 4500</v>
       </c>
       <c r="E6" s="4">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="F6" s="5">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G6" s="1">
-        <v>450300</v>
+        <v>1106000</v>
       </c>
       <c r="H6" s="1">
-        <v>80000</v>
+        <v>200000</v>
       </c>
       <c r="I6" s="1">
-        <v>35000</v>
+        <v>90000</v>
       </c>
       <c r="J6" s="1">
-        <v>1415300</v>
+        <v>2246000</v>
       </c>
       <c r="K6" s="5">
-        <v>42000</v>
+        <v>22000</v>
       </c>
       <c r="L6" s="5">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="M6" s="1">
-        <v>1050000</v>
+        <v>4520000</v>
       </c>
       <c r="N6" s="5">
-        <v>150</v>
+        <v>850</v>
       </c>
       <c r="O6" s="1">
-        <v>2700</v>
+        <v>4200</v>
       </c>
       <c r="P6" s="1">
-        <v>1300</v>
+        <v>1650</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.5185185185185185</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="R6" s="5">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7">
@@ -2325,55 +2325,55 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Vitacura · Alonso de Córdova</v>
+        <v>Ñuñoa · Plaza Ñuñoa</v>
       </c>
       <c r="C7" t="str">
-        <v>Vitacura</v>
+        <v>Ñuñoa</v>
       </c>
       <c r="D7" t="str">
-        <v>Alonso de Córdova 3000 - 4500</v>
+        <v>Av. Irarrázaval 2700 - 3200</v>
       </c>
       <c r="E7" s="4">
-        <v>0.8</v>
+        <v>0.48</v>
       </c>
       <c r="F7" s="5">
         <v>35</v>
       </c>
       <c r="G7" s="1">
-        <v>1106000</v>
+        <v>663600</v>
       </c>
       <c r="H7" s="1">
-        <v>200000</v>
+        <v>110000</v>
       </c>
       <c r="I7" s="1">
-        <v>90000</v>
+        <v>50000</v>
       </c>
       <c r="J7" s="1">
-        <v>2246000</v>
+        <v>1673600</v>
       </c>
       <c r="K7" s="5">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="L7" s="5">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="M7" s="1">
-        <v>4520000</v>
+        <v>1990000</v>
       </c>
       <c r="N7" s="5">
-        <v>850</v>
+        <v>320</v>
       </c>
       <c r="O7" s="1">
-        <v>4200</v>
+        <v>3300</v>
       </c>
       <c r="P7" s="1">
-        <v>1650</v>
+        <v>1400</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.6071428571428571</v>
+        <v>0.5757575757575758</v>
       </c>
       <c r="R7" s="5">
-        <v>70</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8">
@@ -2381,55 +2381,55 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Ñuñoa · Plaza Ñuñoa</v>
+        <v>Estación Central · USACH</v>
       </c>
       <c r="C8" t="str">
-        <v>Ñuñoa</v>
+        <v>Estación Central</v>
       </c>
       <c r="D8" t="str">
-        <v>Av. Irarrázaval 2700 - 3200</v>
+        <v>Av. Bdo OHiggins 3300 - 3700</v>
       </c>
       <c r="E8" s="4">
-        <v>0.48</v>
+        <v>0.38</v>
       </c>
       <c r="F8" s="5">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G8" s="1">
-        <v>663600</v>
+        <v>450300</v>
       </c>
       <c r="H8" s="1">
-        <v>110000</v>
+        <v>80000</v>
       </c>
       <c r="I8" s="1">
-        <v>50000</v>
+        <v>35000</v>
       </c>
       <c r="J8" s="1">
-        <v>1673600</v>
+        <v>1415300</v>
       </c>
       <c r="K8" s="5">
-        <v>24000</v>
+        <v>42000</v>
       </c>
       <c r="L8" s="5">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="M8" s="1">
-        <v>1990000</v>
+        <v>1050000</v>
       </c>
       <c r="N8" s="5">
-        <v>320</v>
+        <v>150</v>
       </c>
       <c r="O8" s="1">
-        <v>3300</v>
+        <v>2700</v>
       </c>
       <c r="P8" s="1">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.5757575757575758</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="R8" s="5">
-        <v>80</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -2461,22 +2461,22 @@
         <v>El Golf</v>
       </c>
       <c r="C1" t="str">
+        <v>Providencia</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Apoquindo / El Bosque</v>
+      </c>
+      <c r="E1" t="str">
         <v>Santiago Centro</v>
       </c>
-      <c r="D1" t="str">
-        <v>Providencia</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Apoquindo / El Bosque</v>
-      </c>
       <c r="F1" t="str">
+        <v>Vitacura</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Ñuñoa</v>
+      </c>
+      <c r="H1" t="str">
         <v>Estación Central</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Vitacura</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Ñuñoa</v>
       </c>
     </row>
     <row r="2">
@@ -2487,22 +2487,22 @@
         <v>0.95</v>
       </c>
       <c r="C2" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E2" s="4">
         <v>0.55</v>
       </c>
-      <c r="D2" s="4">
-        <v>0.65</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0.75</v>
-      </c>
       <c r="F2" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0.48</v>
+      </c>
+      <c r="H2" s="4">
         <v>0.38</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="H2" s="4">
-        <v>0.48</v>
       </c>
     </row>
     <row r="3">
@@ -2513,22 +2513,22 @@
         <v>1313375</v>
       </c>
       <c r="C3" s="1">
+        <v>898625</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1036875</v>
+      </c>
+      <c r="E3" s="1">
         <v>651750</v>
       </c>
-      <c r="D3" s="1">
-        <v>898625</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1036875</v>
-      </c>
       <c r="F3" s="1">
+        <v>1106000</v>
+      </c>
+      <c r="G3" s="1">
+        <v>663600</v>
+      </c>
+      <c r="H3" s="1">
         <v>450300</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1106000</v>
-      </c>
-      <c r="H3" s="1">
-        <v>663600</v>
       </c>
     </row>
     <row r="4">
@@ -2539,22 +2539,22 @@
         <v>220000</v>
       </c>
       <c r="C4" s="1">
+        <v>150000</v>
+      </c>
+      <c r="D4" s="1">
+        <v>180000</v>
+      </c>
+      <c r="E4" s="1">
         <v>140000</v>
       </c>
-      <c r="D4" s="1">
-        <v>150000</v>
-      </c>
-      <c r="E4" s="1">
-        <v>180000</v>
-      </c>
       <c r="F4" s="1">
+        <v>200000</v>
+      </c>
+      <c r="G4" s="1">
+        <v>110000</v>
+      </c>
+      <c r="H4" s="1">
         <v>80000</v>
-      </c>
-      <c r="G4" s="1">
-        <v>200000</v>
-      </c>
-      <c r="H4" s="1">
-        <v>110000</v>
       </c>
     </row>
     <row r="5">
@@ -2565,22 +2565,22 @@
         <v>95000</v>
       </c>
       <c r="C5" s="1">
+        <v>65000</v>
+      </c>
+      <c r="D5" s="1">
+        <v>75000</v>
+      </c>
+      <c r="E5" s="1">
         <v>55000</v>
       </c>
-      <c r="D5" s="1">
-        <v>65000</v>
-      </c>
-      <c r="E5" s="1">
-        <v>75000</v>
-      </c>
       <c r="F5" s="1">
+        <v>90000</v>
+      </c>
+      <c r="G5" s="1">
+        <v>50000</v>
+      </c>
+      <c r="H5" s="1">
         <v>35000</v>
-      </c>
-      <c r="G5" s="1">
-        <v>90000</v>
-      </c>
-      <c r="H5" s="1">
-        <v>50000</v>
       </c>
     </row>
     <row r="6">
@@ -2721,22 +2721,22 @@
         <v>2478375</v>
       </c>
       <c r="C11" s="1">
+        <v>1963625</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2141875</v>
+      </c>
+      <c r="E11" s="1">
         <v>1696750</v>
       </c>
-      <c r="D11" s="1">
-        <v>1963625</v>
-      </c>
-      <c r="E11" s="1">
-        <v>2141875</v>
-      </c>
       <c r="F11" s="1">
+        <v>2246000</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1673600</v>
+      </c>
+      <c r="H11" s="1">
         <v>1415300</v>
-      </c>
-      <c r="G11" s="1">
-        <v>2246000</v>
-      </c>
-      <c r="H11" s="1">
-        <v>1673600</v>
       </c>
     </row>
     <row r="13">
@@ -2773,22 +2773,22 @@
         <v>5420822</v>
       </c>
       <c r="C15" s="1">
+        <v>4906072</v>
+      </c>
+      <c r="D15" s="1">
+        <v>5084322</v>
+      </c>
+      <c r="E15" s="1">
         <v>4639197</v>
       </c>
-      <c r="D15" s="1">
-        <v>4906072</v>
-      </c>
-      <c r="E15" s="1">
-        <v>5084322</v>
-      </c>
       <c r="F15" s="1">
+        <v>5188447</v>
+      </c>
+      <c r="G15" s="1">
+        <v>4616047</v>
+      </c>
+      <c r="H15" s="1">
         <v>4357747</v>
-      </c>
-      <c r="G15" s="1">
-        <v>5188447</v>
-      </c>
-      <c r="H15" s="1">
-        <v>4616047</v>
       </c>
     </row>
     <row r="16">
@@ -2799,22 +2799,22 @@
         <v>65049864</v>
       </c>
       <c r="C16" s="1">
+        <v>58872864</v>
+      </c>
+      <c r="D16" s="1">
+        <v>61011864</v>
+      </c>
+      <c r="E16" s="1">
         <v>55670364</v>
       </c>
-      <c r="D16" s="1">
-        <v>58872864</v>
-      </c>
-      <c r="E16" s="1">
-        <v>61011864</v>
-      </c>
       <c r="F16" s="1">
+        <v>62261364</v>
+      </c>
+      <c r="G16" s="1">
+        <v>55392564</v>
+      </c>
+      <c r="H16" s="1">
         <v>52292964</v>
-      </c>
-      <c r="G16" s="1">
-        <v>62261364</v>
-      </c>
-      <c r="H16" s="1">
-        <v>55392564</v>
       </c>
     </row>
     <row r="18">
@@ -2825,22 +2825,22 @@
         <v>1700</v>
       </c>
       <c r="C18" s="1">
+        <v>1500</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1550</v>
+      </c>
+      <c r="E18" s="1">
         <v>1350</v>
       </c>
-      <c r="D18" s="1">
-        <v>1500</v>
-      </c>
-      <c r="E18" s="1">
-        <v>1550</v>
-      </c>
       <c r="F18" s="1">
+        <v>1650</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1400</v>
+      </c>
+      <c r="H18" s="1">
         <v>1300</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1650</v>
-      </c>
-      <c r="H18" s="1">
-        <v>1400</v>
       </c>
     </row>
     <row r="19">
@@ -2848,25 +2848,25 @@
         <v>Ingresos anuales caso base</v>
       </c>
       <c r="B19" s="1">
-        <v>133380000</v>
+        <v>216216000</v>
       </c>
       <c r="C19" s="1">
-        <v>117624000</v>
+        <v>210100800</v>
       </c>
       <c r="D19" s="1">
-        <v>109668000</v>
+        <v>187324800</v>
       </c>
       <c r="E19" s="1">
-        <v>106704000</v>
+        <v>189103200</v>
       </c>
       <c r="F19" s="1">
-        <v>92664000</v>
+        <v>158558400</v>
       </c>
       <c r="G19" s="1">
-        <v>91728000</v>
+        <v>143114400</v>
       </c>
       <c r="H19" s="1">
-        <v>82368000</v>
+        <v>123832800</v>
       </c>
     </row>
     <row r="20">
@@ -2874,25 +2874,25 @@
         <v>Costos variables anuales caso base</v>
       </c>
       <c r="B20" s="1">
-        <v>50388000</v>
+        <v>81681600</v>
       </c>
       <c r="C20" s="1">
-        <v>54756000</v>
+        <v>85176000</v>
       </c>
       <c r="D20" s="1">
-        <v>44460000</v>
+        <v>76408800</v>
       </c>
       <c r="E20" s="1">
-        <v>43524000</v>
+        <v>88030800</v>
       </c>
       <c r="F20" s="1">
-        <v>44616000</v>
+        <v>62290800</v>
       </c>
       <c r="G20" s="1">
-        <v>36036000</v>
+        <v>60715200</v>
       </c>
       <c r="H20" s="1">
-        <v>34944000</v>
+        <v>59623200</v>
       </c>
     </row>
     <row r="21">
@@ -2900,25 +2900,25 @@
         <v>Comisión tarjetas (2.8%)</v>
       </c>
       <c r="B21" s="1">
-        <v>3734640</v>
+        <v>6054048</v>
       </c>
       <c r="C21" s="1">
-        <v>3293472</v>
+        <v>5882822.4</v>
       </c>
       <c r="D21" s="1">
-        <v>3070704</v>
+        <v>5245094.4</v>
       </c>
       <c r="E21" s="1">
-        <v>2987712</v>
+        <v>5294889.600000001</v>
       </c>
       <c r="F21" s="1">
-        <v>2594592</v>
+        <v>4439635.2</v>
       </c>
       <c r="G21" s="1">
-        <v>2568384</v>
+        <v>4007203.2</v>
       </c>
       <c r="H21" s="1">
-        <v>2306304</v>
+        <v>3467318.4</v>
       </c>
     </row>
     <row r="22">
@@ -2929,22 +2929,22 @@
         <v>2800</v>
       </c>
       <c r="C22" s="1">
+        <v>2200</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2250</v>
+      </c>
+      <c r="E22" s="1">
         <v>1550</v>
       </c>
-      <c r="D22" s="1">
-        <v>2200</v>
-      </c>
-      <c r="E22" s="1">
-        <v>2250</v>
-      </c>
       <c r="F22" s="1">
+        <v>2550</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1900</v>
+      </c>
+      <c r="H22" s="1">
         <v>1400</v>
-      </c>
-      <c r="G22" s="1">
-        <v>2550</v>
-      </c>
-      <c r="H22" s="1">
-        <v>1900</v>
       </c>
     </row>
     <row r="23">
@@ -2955,22 +2955,22 @@
         <v>0.6222222222222222</v>
       </c>
       <c r="C23" s="2">
+        <v>0.5945945945945946</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0.5921052631578947</v>
+      </c>
+      <c r="E23" s="2">
         <v>0.5344827586206896</v>
       </c>
-      <c r="D23" s="2">
-        <v>0.5945945945945946</v>
-      </c>
-      <c r="E23" s="2">
-        <v>0.5921052631578947</v>
-      </c>
       <c r="F23" s="2">
+        <v>0.6071428571428571</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="H23" s="2">
         <v>0.5185185185185185</v>
-      </c>
-      <c r="G23" s="2">
-        <v>0.6071428571428571</v>
-      </c>
-      <c r="H23" s="2">
-        <v>0.5757575757575758</v>
       </c>
     </row>
     <row r="24">
@@ -2978,25 +2978,25 @@
         <v>EBITDA año 1</v>
       </c>
       <c r="B24" s="1">
-        <v>14207499</v>
+        <v>5614332</v>
       </c>
       <c r="C24" s="1">
-        <v>3904167</v>
+        <v>6600226</v>
       </c>
       <c r="D24" s="1">
-        <v>3264435</v>
+        <v>-2892863</v>
       </c>
       <c r="E24" s="1">
-        <v>-819573</v>
+        <v>-2992731</v>
       </c>
       <c r="F24" s="1">
-        <v>-6839553</v>
+        <v>-11755981</v>
       </c>
       <c r="G24" s="1">
-        <v>-9137745</v>
+        <v>-12276963</v>
       </c>
       <c r="H24" s="1">
-        <v>-10274865</v>
+        <v>-18884706</v>
       </c>
     </row>
   </sheetData>
@@ -3718,34 +3718,34 @@
         <v>Las Condes</v>
       </c>
       <c r="D2">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="E2" s="1">
-        <v>44549554</v>
+        <v>51069054</v>
       </c>
       <c r="F2" s="1">
-        <v>14207499</v>
+        <v>5614332</v>
       </c>
       <c r="G2" s="1">
-        <v>48686717</v>
+        <v>161650312</v>
       </c>
       <c r="H2" s="1">
-        <v>-85083211</v>
+        <v>8545615</v>
       </c>
       <c r="I2" s="1">
-        <v>169302451</v>
+        <v>298901997</v>
       </c>
       <c r="J2" s="2">
-        <v>0.3897448098295899</v>
+        <v>0.6245770437265755</v>
       </c>
       <c r="K2">
-        <v>3.39</v>
+        <v>2.57</v>
       </c>
       <c r="L2">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M2" t="str">
-        <v>Aceptable con riesgo</v>
+        <v>Recomendado</v>
       </c>
     </row>
     <row r="3">
@@ -3753,40 +3753,40 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Santiago Centro · Ahumada</v>
+        <v>Providencia · Pedro de Valdivia</v>
       </c>
       <c r="C3" t="str">
-        <v>Santiago</v>
+        <v>Providencia</v>
       </c>
       <c r="D3">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="E3" s="1">
-        <v>43505492</v>
+        <v>50510179</v>
       </c>
       <c r="F3" s="1">
-        <v>3904167</v>
+        <v>6600226</v>
       </c>
       <c r="G3" s="1">
-        <v>3570276</v>
+        <v>154338627</v>
       </c>
       <c r="H3" s="1">
-        <v>-107540017</v>
+        <v>9489071</v>
       </c>
       <c r="I3" s="1">
-        <v>135165983</v>
+        <v>275421162</v>
       </c>
       <c r="J3" s="2">
-        <v>0.16143628907794347</v>
+        <v>0.616604428708901</v>
       </c>
       <c r="K3">
-        <v>4.36</v>
+        <v>2.58</v>
       </c>
       <c r="L3">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="M3" t="str">
-        <v>No conviene</v>
+        <v>Recomendado</v>
       </c>
     </row>
     <row r="4">
@@ -3794,40 +3794,40 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Providencia · Pedro de Valdivia</v>
+        <v>Apoquindo / El Bosque · Las Condes</v>
       </c>
       <c r="C4" t="str">
-        <v>Providencia</v>
+        <v>Las Condes</v>
       </c>
       <c r="D4">
-        <v>95</v>
+        <v>158</v>
       </c>
       <c r="E4" s="1">
-        <v>42027679</v>
+        <v>49129304</v>
       </c>
       <c r="F4" s="1">
-        <v>3264435</v>
+        <v>-2892863</v>
       </c>
       <c r="G4" s="1">
-        <v>2417700</v>
+        <v>98709622</v>
       </c>
       <c r="H4" s="1">
-        <v>-109507512</v>
+        <v>-36138011</v>
       </c>
       <c r="I4" s="1">
-        <v>123762360</v>
+        <v>201743858</v>
       </c>
       <c r="J4" s="2">
-        <v>0.15502872448589966</v>
+        <v>0.4691992318618286</v>
       </c>
       <c r="K4">
-        <v>4.38</v>
+        <v>3.3</v>
       </c>
       <c r="L4">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="M4" t="str">
-        <v>No conviene</v>
+        <v>Aceptable con riesgo</v>
       </c>
     </row>
     <row r="5">
@@ -3835,40 +3835,40 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Apoquindo / El Bosque · Las Condes</v>
+        <v>Santiago Centro · Ahumada</v>
       </c>
       <c r="C5" t="str">
-        <v>Las Condes</v>
+        <v>Santiago</v>
       </c>
       <c r="D5">
-        <v>90</v>
+        <v>209</v>
       </c>
       <c r="E5" s="1">
-        <v>42278304</v>
+        <v>50437742</v>
       </c>
       <c r="F5" s="1">
-        <v>-819573</v>
+        <v>-2992731</v>
       </c>
       <c r="G5" s="1">
-        <v>-14887101</v>
+        <v>87093900</v>
       </c>
       <c r="H5" s="1">
-        <v>-132358431</v>
+        <v>-39379309</v>
       </c>
       <c r="I5" s="1">
-        <v>95985669</v>
+        <v>192412756</v>
       </c>
       <c r="J5" s="2">
-        <v>0.04255006204542362</v>
+        <v>0.4328719148703745</v>
       </c>
       <c r="K5">
-        <v>4.79</v>
+        <v>3.51</v>
       </c>
       <c r="L5">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="M5" t="str">
-        <v>No conviene</v>
+        <v>Aceptable con riesgo</v>
       </c>
     </row>
     <row r="6">
@@ -3876,37 +3876,40 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Estación Central · USACH</v>
+        <v>Vitacura · Alonso de Córdova</v>
       </c>
       <c r="C6" t="str">
-        <v>Estación Central</v>
+        <v>Vitacura</v>
       </c>
       <c r="D6">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E6" s="1">
-        <v>40689367</v>
+        <v>46448367</v>
       </c>
       <c r="F6" s="1">
-        <v>-6839553</v>
+        <v>-11755981</v>
       </c>
       <c r="G6" s="1">
-        <v>-47336647</v>
+        <v>46270049</v>
       </c>
       <c r="H6" s="1">
-        <v>-150485289</v>
+        <v>-76006860</v>
       </c>
       <c r="I6" s="1">
-        <v>77473401</v>
-      </c>
-      <c r="K6" t="str">
-        <v>&gt; 5</v>
+        <v>143017713</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.3117614263631726</v>
+      </c>
+      <c r="K6">
+        <v>4.07</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="M6" t="str">
-        <v>No conviene</v>
+        <v>Aceptable con riesgo</v>
       </c>
     </row>
     <row r="7">
@@ -3914,37 +3917,40 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Vitacura · Alonso de Córdova</v>
+        <v>Ñuñoa · Plaza Ñuñoa</v>
       </c>
       <c r="C7" t="str">
-        <v>Vitacura</v>
+        <v>Ñuñoa</v>
       </c>
       <c r="D7">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="E7" s="1">
-        <v>40978617</v>
+        <v>44689117</v>
       </c>
       <c r="F7" s="1">
-        <v>-9137745</v>
+        <v>-12276963</v>
       </c>
       <c r="G7" s="1">
-        <v>-56240799</v>
+        <v>27541729</v>
       </c>
       <c r="H7" s="1">
-        <v>-170598091</v>
+        <v>-78151616</v>
       </c>
       <c r="I7" s="1">
-        <v>61375831</v>
-      </c>
-      <c r="K7" t="str">
-        <v>&gt; 5</v>
+        <v>107294736</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.25184266824949386</v>
+      </c>
+      <c r="K7">
+        <v>4.18</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M7" t="str">
-        <v>No conviene</v>
+        <v>Aceptable con riesgo</v>
       </c>
     </row>
     <row r="8">
@@ -3952,34 +3958,37 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Ñuñoa · Plaza Ñuñoa</v>
+        <v>Estación Central · USACH</v>
       </c>
       <c r="C8" t="str">
-        <v>Ñuñoa</v>
+        <v>Estación Central</v>
       </c>
       <c r="D8">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="E8" s="1">
-        <v>39320117</v>
+        <v>43815867</v>
       </c>
       <c r="F8" s="1">
-        <v>-10274865</v>
+        <v>-18884706</v>
       </c>
       <c r="G8" s="1">
-        <v>-63254582</v>
+        <v>-23503844</v>
       </c>
       <c r="H8" s="1">
-        <v>-148074497</v>
+        <v>-108796299</v>
       </c>
       <c r="I8" s="1">
-        <v>38908893</v>
-      </c>
-      <c r="K8" t="str">
-        <v>&gt; 5</v>
+        <v>45745411</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.030230875745438653</v>
+      </c>
+      <c r="K8">
+        <v>4.86</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M8" t="str">
         <v>No conviene</v>
@@ -4012,7 +4021,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>VAN 48.686.717  ·  TIR 39.0%  ·  Payback 3.39 años</v>
+        <v>VAN 161.650.312  ·  TIR 62.5%  ·  Payback 2.57 años</v>
       </c>
     </row>
     <row r="4">
@@ -4046,19 +4055,19 @@
         <v/>
       </c>
       <c r="C5" s="5">
-        <v>29640</v>
+        <v>26426</v>
       </c>
       <c r="D5" s="5">
-        <v>30381</v>
+        <v>36036</v>
       </c>
       <c r="E5" s="5">
-        <v>31141</v>
+        <v>43243</v>
       </c>
       <c r="F5" s="5">
-        <v>31919</v>
+        <v>48048</v>
       </c>
       <c r="G5" s="5">
-        <v>32717</v>
+        <v>49249</v>
       </c>
     </row>
     <row r="6">
@@ -4069,19 +4078,19 @@
         <v/>
       </c>
       <c r="C6" s="1">
-        <v>133380000</v>
+        <v>118918800</v>
       </c>
       <c r="D6" s="1">
-        <v>136714499.99999997</v>
+        <v>162162000</v>
       </c>
       <c r="E6" s="1">
-        <v>140132362.5</v>
+        <v>194594400.00000003</v>
       </c>
       <c r="F6" s="1">
-        <v>143635671.56249994</v>
+        <v>216216000</v>
       </c>
       <c r="G6" s="1">
-        <v>147226563.35156244</v>
+        <v>221621400</v>
       </c>
     </row>
     <row r="7">
@@ -4092,19 +4101,19 @@
         <v/>
       </c>
       <c r="C7" s="1">
-        <v>-50388000</v>
+        <v>-44924880</v>
       </c>
       <c r="D7" s="1">
-        <v>-51647699.99999999</v>
+        <v>-61261200</v>
       </c>
       <c r="E7" s="1">
-        <v>-52938892.5</v>
+        <v>-73513440</v>
       </c>
       <c r="F7" s="1">
-        <v>-54262364.81249998</v>
+        <v>-81681600</v>
       </c>
       <c r="G7" s="1">
-        <v>-55618923.932812475</v>
+        <v>-83723640</v>
       </c>
     </row>
     <row r="8">
@@ -4138,19 +4147,19 @@
         <v/>
       </c>
       <c r="C9" s="1">
-        <v>-3734640</v>
+        <v>-3329726.4</v>
       </c>
       <c r="D9" s="1">
-        <v>-3828005.999999999</v>
+        <v>-4540536</v>
       </c>
       <c r="E9" s="1">
-        <v>-3923706.15</v>
+        <v>-5448643.200000001</v>
       </c>
       <c r="F9" s="1">
-        <v>-4021798.8037499986</v>
+        <v>-6054048</v>
       </c>
       <c r="G9" s="1">
-        <v>-4122343.7738437485</v>
+        <v>-6205399.2</v>
       </c>
     </row>
     <row r="10">
@@ -4161,19 +4170,19 @@
         <v/>
       </c>
       <c r="C10" s="1">
-        <v>14207498.6448</v>
+        <v>5614332.2447999995</v>
       </c>
       <c r="D10" s="1">
-        <v>16188932.64479997</v>
+        <v>31310402.6448</v>
       </c>
       <c r="E10" s="1">
-        <v>18219902.4948</v>
+        <v>50582455.44480003</v>
       </c>
       <c r="F10" s="1">
-        <v>20301646.591049973</v>
+        <v>63430490.64480001</v>
       </c>
       <c r="G10" s="1">
-        <v>22435434.289706208</v>
+        <v>66642499.444800004</v>
       </c>
     </row>
     <row r="11">
@@ -4207,19 +4216,19 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>11644998.6448</v>
+        <v>3051832.2447999995</v>
       </c>
       <c r="D12" s="1">
-        <v>13626432.64479997</v>
+        <v>28747902.6448</v>
       </c>
       <c r="E12" s="1">
-        <v>15657402.494800001</v>
+        <v>48019955.44480003</v>
       </c>
       <c r="F12" s="1">
-        <v>17739146.591049973</v>
+        <v>60867990.64480001</v>
       </c>
       <c r="G12" s="1">
-        <v>19872934.289706208</v>
+        <v>64079999.444800004</v>
       </c>
     </row>
     <row r="13">
@@ -4230,19 +4239,19 @@
         <v/>
       </c>
       <c r="C13" s="1">
-        <v>-2911249.6612</v>
+        <v>-762958.0611999999</v>
       </c>
       <c r="D13" s="1">
-        <v>-3406608.1611999925</v>
+        <v>-7186975.6612</v>
       </c>
       <c r="E13" s="1">
-        <v>-3914350.6237000003</v>
+        <v>-12004988.861200007</v>
       </c>
       <c r="F13" s="1">
-        <v>-4434786.647762493</v>
+        <v>-15216997.661200002</v>
       </c>
       <c r="G13" s="1">
-        <v>-4968233.572426552</v>
+        <v>-16019999.861200001</v>
       </c>
     </row>
     <row r="14">
@@ -4253,19 +4262,19 @@
         <v/>
       </c>
       <c r="C14" s="1">
-        <v>8733748.9836</v>
+        <v>2288874.1835999996</v>
       </c>
       <c r="D14" s="1">
-        <v>10219824.483599978</v>
+        <v>21560926.983599998</v>
       </c>
       <c r="E14" s="1">
-        <v>11743051.871100001</v>
+        <v>36014966.58360002</v>
       </c>
       <c r="F14" s="1">
-        <v>13304359.94328748</v>
+        <v>45650992.983600006</v>
       </c>
       <c r="G14" s="1">
-        <v>14904700.717279656</v>
+        <v>48059999.5836</v>
       </c>
     </row>
     <row r="15">
@@ -4299,19 +4308,19 @@
         <v/>
       </c>
       <c r="C16" s="1">
-        <v>11296248.9836</v>
+        <v>4851374.183599999</v>
       </c>
       <c r="D16" s="1">
-        <v>12782324.483599978</v>
+        <v>24123426.983599998</v>
       </c>
       <c r="E16" s="1">
-        <v>14305551.871100001</v>
+        <v>38577466.58360002</v>
       </c>
       <c r="F16" s="1">
-        <v>15866859.94328748</v>
+        <v>48213492.983600006</v>
       </c>
       <c r="G16" s="1">
-        <v>17467200.717279658</v>
+        <v>50622499.5836</v>
       </c>
     </row>
     <row r="17">
@@ -4334,7 +4343,7 @@
         <v/>
       </c>
       <c r="G17" s="1">
-        <v>24049554</v>
+        <v>30569054</v>
       </c>
     </row>
     <row r="18">
@@ -4380,7 +4389,7 @@
         <v/>
       </c>
       <c r="G19" s="1">
-        <v>58893015.010478795</v>
+        <v>174936561.0426</v>
       </c>
     </row>
     <row r="20">
@@ -4411,7 +4420,7 @@
         <v>(-) Capital de trabajo</v>
       </c>
       <c r="B21" s="1">
-        <v>-24049554</v>
+        <v>-30569054</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -4434,22 +4443,22 @@
         <v>FLUJO NETO DE CAJA</v>
       </c>
       <c r="B22" s="1">
-        <v>-44549554</v>
+        <v>-51069054</v>
       </c>
       <c r="C22" s="1">
-        <v>11296248.9836</v>
+        <v>4851374.183599999</v>
       </c>
       <c r="D22" s="1">
-        <v>12782324.483599978</v>
+        <v>24123426.983599998</v>
       </c>
       <c r="E22" s="1">
-        <v>14305551.871100001</v>
+        <v>38577466.58360002</v>
       </c>
       <c r="F22" s="1">
-        <v>15866859.94328748</v>
+        <v>48213492.983600006</v>
       </c>
       <c r="G22" s="1">
-        <v>104822269.72775845</v>
+        <v>260540614.62620002</v>
       </c>
     </row>
     <row r="24">
@@ -4462,7 +4471,7 @@
         <v>VAN</v>
       </c>
       <c r="B25" s="1">
-        <v>48686717</v>
+        <v>161650312</v>
       </c>
     </row>
     <row r="26">
@@ -4470,7 +4479,7 @@
         <v>TIR</v>
       </c>
       <c r="B26" s="2">
-        <v>0.3897448098295899</v>
+        <v>0.6245770437265755</v>
       </c>
     </row>
     <row r="27">
@@ -4478,7 +4487,7 @@
         <v>Payback (años)</v>
       </c>
       <c r="B27">
-        <v>3.3885727033412385</v>
+        <v>2.572724307463795</v>
       </c>
     </row>
     <row r="28">
@@ -4531,7 +4540,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>VAN base: $48.686.717</v>
+        <v>VAN base: $161.650.312</v>
       </c>
     </row>
     <row r="4">
@@ -4559,19 +4568,19 @@
         <v>Ticket promedio</v>
       </c>
       <c r="B5" s="1">
-        <v>-70289986</v>
+        <v>13571996</v>
       </c>
       <c r="C5" s="1">
-        <v>-5749468</v>
+        <v>88053151</v>
       </c>
       <c r="D5" s="1">
-        <v>48686717</v>
+        <v>161650312</v>
       </c>
       <c r="E5" s="1">
-        <v>103064172</v>
+        <v>235018365</v>
       </c>
       <c r="F5" s="1">
-        <v>157441628</v>
+        <v>308386418</v>
       </c>
     </row>
     <row r="6">
@@ -4579,19 +4588,19 @@
         <v>Demanda (combos/día)</v>
       </c>
       <c r="B6" s="1">
-        <v>-17977794</v>
+        <v>73244133</v>
       </c>
       <c r="C6" s="1">
-        <v>15948161</v>
+        <v>117507277</v>
       </c>
       <c r="D6" s="1">
-        <v>48686717</v>
+        <v>161650312</v>
       </c>
       <c r="E6" s="1">
-        <v>81425274</v>
+        <v>205685227</v>
       </c>
       <c r="F6" s="1">
-        <v>114163830</v>
+        <v>249720143</v>
       </c>
     </row>
     <row r="7">
@@ -4599,19 +4608,19 @@
         <v>Costo variable insumo</v>
       </c>
       <c r="B7" s="1">
-        <v>91964515</v>
+        <v>220316586</v>
       </c>
       <c r="C7" s="1">
-        <v>70325616</v>
+        <v>190983449</v>
       </c>
       <c r="D7" s="1">
-        <v>48686717</v>
+        <v>161650312</v>
       </c>
       <c r="E7" s="1">
-        <v>27047818</v>
+        <v>132278375</v>
       </c>
       <c r="F7" s="1">
-        <v>5408919</v>
+        <v>102824249</v>
       </c>
     </row>
     <row r="8">
@@ -4619,19 +4628,19 @@
         <v>Arriendo UF/m²</v>
       </c>
       <c r="B8" s="1">
-        <v>61415795</v>
+        <v>174379389</v>
       </c>
       <c r="C8" s="1">
-        <v>55051256</v>
+        <v>168014850</v>
       </c>
       <c r="D8" s="1">
-        <v>48686717</v>
+        <v>161650312</v>
       </c>
       <c r="E8" s="1">
-        <v>42322178</v>
+        <v>155285772</v>
       </c>
       <c r="F8" s="1">
-        <v>35957639</v>
+        <v>148918533</v>
       </c>
     </row>
     <row r="9">
@@ -4639,19 +4648,19 @@
         <v>Sueldos planilla</v>
       </c>
       <c r="B9" s="1">
-        <v>66869701</v>
+        <v>179833296</v>
       </c>
       <c r="C9" s="1">
-        <v>57778209</v>
+        <v>170741804</v>
       </c>
       <c r="D9" s="1">
-        <v>48686717</v>
+        <v>161650312</v>
       </c>
       <c r="E9" s="1">
-        <v>39595225</v>
+        <v>152558820</v>
       </c>
       <c r="F9" s="1">
-        <v>30503733</v>
+        <v>143467328</v>
       </c>
     </row>
     <row r="11">
@@ -4684,19 +4693,19 @@
         <v>Ticket promedio</v>
       </c>
       <c r="B13" s="1">
-        <v>-118976703</v>
+        <v>-148078316</v>
       </c>
       <c r="C13" s="1">
-        <v>-54436185</v>
+        <v>-73597161</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>54377455</v>
+        <v>73368053</v>
       </c>
       <c r="F13" s="1">
-        <v>108754911</v>
+        <v>146736106</v>
       </c>
     </row>
     <row r="14">
@@ -4704,19 +4713,19 @@
         <v>Demanda (combos/día)</v>
       </c>
       <c r="B14" s="1">
-        <v>-66664511</v>
+        <v>-88406179</v>
       </c>
       <c r="C14" s="1">
-        <v>-32738556</v>
+        <v>-44143035</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>32738557</v>
+        <v>44034915</v>
       </c>
       <c r="F14" s="1">
-        <v>65477113</v>
+        <v>88069831</v>
       </c>
     </row>
     <row r="15">
@@ -4724,19 +4733,19 @@
         <v>Costo variable insumo</v>
       </c>
       <c r="B15" s="1">
-        <v>43277798</v>
+        <v>58666274</v>
       </c>
       <c r="C15" s="1">
-        <v>21638899</v>
+        <v>29333137</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>-21638899</v>
+        <v>-29371937</v>
       </c>
       <c r="F15" s="1">
-        <v>-43277798</v>
+        <v>-58826063</v>
       </c>
     </row>
     <row r="16">
@@ -4764,19 +4773,19 @@
         <v>Arriendo UF/m²</v>
       </c>
       <c r="B17" s="1">
-        <v>12729078</v>
+        <v>12729077</v>
       </c>
       <c r="C17" s="1">
-        <v>6364539</v>
+        <v>6364538</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>-6364539</v>
+        <v>-6364540</v>
       </c>
       <c r="F17" s="1">
-        <v>-12729078</v>
+        <v>-12731779</v>
       </c>
     </row>
   </sheetData>

--- a/public/exports/Analisis_Cafe_Combo_RM.xlsx
+++ b/public/exports/Analisis_Cafe_Combo_RM.xlsx
@@ -475,7 +475,7 @@
         <v>VAN base</v>
       </c>
       <c r="B11" s="1">
-        <v>161650312</v>
+        <v>107168913</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +483,7 @@
         <v>TIR base</v>
       </c>
       <c r="B12" s="2">
-        <v>0.6245770437265755</v>
+        <v>0.48968545245506934</v>
       </c>
     </row>
     <row r="13">
@@ -491,7 +491,7 @@
         <v>Payback (años)</v>
       </c>
       <c r="B13">
-        <v>2.572724307463795</v>
+        <v>3.2084580369294096</v>
       </c>
     </row>
     <row r="14">
@@ -499,7 +499,7 @@
         <v>Inversión total</v>
       </c>
       <c r="B14" s="1">
-        <v>51069054</v>
+        <v>48969554</v>
       </c>
     </row>
     <row r="15">
@@ -507,7 +507,7 @@
         <v>EBITDA año 1</v>
       </c>
       <c r="B15" s="1">
-        <v>5614332</v>
+        <v>-3103977</v>
       </c>
     </row>
     <row r="16">
@@ -515,7 +515,7 @@
         <v>Veredicto</v>
       </c>
       <c r="B16" t="str">
-        <v>Recomendado</v>
+        <v>Aceptable con riesgo</v>
       </c>
     </row>
     <row r="17">
@@ -523,7 +523,7 @@
         <v>Score de viabilidad (0-100)</v>
       </c>
       <c r="B17">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19">
@@ -1231,7 +1231,7 @@
         <v>VAN base</v>
       </c>
       <c r="B6" t="str">
-        <v>$161.650.312</v>
+        <v>$107.168.913</v>
       </c>
     </row>
     <row r="7">
@@ -1239,7 +1239,7 @@
         <v>TIR</v>
       </c>
       <c r="B7" t="str">
-        <v>62.5%</v>
+        <v>49.0%</v>
       </c>
     </row>
     <row r="8">
@@ -1247,7 +1247,7 @@
         <v>Payback</v>
       </c>
       <c r="B8" t="str">
-        <v>2.57 años</v>
+        <v>3.21 años</v>
       </c>
     </row>
     <row r="9">
@@ -1255,7 +1255,7 @@
         <v>Inversión inicial</v>
       </c>
       <c r="B9" t="str">
-        <v>$51.069.054</v>
+        <v>$48.969.554</v>
       </c>
     </row>
     <row r="10">
@@ -1263,7 +1263,7 @@
         <v>Combos/día base</v>
       </c>
       <c r="B10">
-        <v>154</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -1271,7 +1271,7 @@
         <v>EBITDA año 1</v>
       </c>
       <c r="B11" t="str">
-        <v>$5.614.332</v>
+        <v>$-3.103.977</v>
       </c>
     </row>
     <row r="12">
@@ -1287,7 +1287,7 @@
         <v>Score viabilidad</v>
       </c>
       <c r="B13" t="str">
-        <v>100 / 100</v>
+        <v>65 / 100</v>
       </c>
     </row>
     <row r="15">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>✅ Recomendadas (6)</v>
+        <v>✅ Recomendadas (5)</v>
       </c>
     </row>
     <row r="21">
@@ -1315,13 +1315,13 @@
         <v>El Golf · Las Condes</v>
       </c>
       <c r="B21" t="str">
-        <v>$161.650.312</v>
+        <v>$107.168.913</v>
       </c>
       <c r="C21" t="str">
-        <v>62.5%</v>
+        <v>49.0%</v>
       </c>
       <c r="D21" t="str">
-        <v>Score 100</v>
+        <v>Score 65</v>
       </c>
     </row>
     <row r="22">
@@ -1329,24 +1329,24 @@
         <v>Providencia · Pedro de Valdivia</v>
       </c>
       <c r="B22" t="str">
-        <v>$154.338.627</v>
+        <v>$46.142.432</v>
       </c>
       <c r="C22" t="str">
-        <v>61.7%</v>
+        <v>31.5%</v>
       </c>
       <c r="D22" t="str">
-        <v>Score 100</v>
+        <v>Score 65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Apoquindo / El Bosque · Las Condes</v>
+        <v>Vitacura · Alonso de Córdova</v>
       </c>
       <c r="B23" t="str">
-        <v>$98.709.622</v>
+        <v>$41.005.310</v>
       </c>
       <c r="C23" t="str">
-        <v>46.9%</v>
+        <v>29.4%</v>
       </c>
       <c r="D23" t="str">
         <v>Score 65</v>
@@ -1354,13 +1354,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Santiago Centro · Ahumada</v>
+        <v>Ñuñoa · Plaza Ñuñoa</v>
       </c>
       <c r="B24" t="str">
-        <v>$87.093.900</v>
+        <v>$27.541.729</v>
       </c>
       <c r="C24" t="str">
-        <v>43.3%</v>
+        <v>25.2%</v>
       </c>
       <c r="D24" t="str">
         <v>Score 65</v>
@@ -1368,49 +1368,49 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Vitacura · Alonso de Córdova</v>
+        <v>Apoquindo / El Bosque · Las Condes</v>
       </c>
       <c r="B25" t="str">
-        <v>$46.270.049</v>
+        <v>$24.702.079</v>
       </c>
       <c r="C25" t="str">
-        <v>31.2%</v>
+        <v>23.6%</v>
       </c>
       <c r="D25" t="str">
         <v>Score 65</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Ñuñoa · Plaza Ñuñoa</v>
-      </c>
-      <c r="B26" t="str">
-        <v>$27.541.729</v>
-      </c>
-      <c r="C26" t="str">
-        <v>25.2%</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Score 65</v>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>❌ No recomendadas (2)</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>❌ No recomendadas (1)</v>
+        <v>Estación Central · USACH</v>
+      </c>
+      <c r="B28" t="str">
+        <v>$-23.503.844</v>
+      </c>
+      <c r="C28" t="str">
+        <v>3.0%</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Score 38</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Estación Central · USACH</v>
+        <v>Santiago Centro · Ahumada</v>
       </c>
       <c r="B29" t="str">
-        <v>$-23.503.844</v>
+        <v>$-58.283.217</v>
       </c>
       <c r="C29" t="str">
-        <v>3.0%</v>
+        <v>—</v>
       </c>
       <c r="D29" t="str">
-        <v>Score 38</v>
+        <v>Score 0</v>
       </c>
     </row>
     <row r="31">
@@ -2093,7 +2093,7 @@
         <v>0.6222222222222222</v>
       </c>
       <c r="R2" s="5">
-        <v>154</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3">
@@ -2149,7 +2149,7 @@
         <v>0.5945945945945946</v>
       </c>
       <c r="R3" s="5">
-        <v>182</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4">
@@ -2157,55 +2157,55 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Apoquindo / El Bosque · Las Condes</v>
+        <v>Vitacura · Alonso de Córdova</v>
       </c>
       <c r="C4" t="str">
-        <v>Las Condes</v>
+        <v>Vitacura</v>
       </c>
       <c r="D4" t="str">
-        <v>Apoquindo 4000 - 4900</v>
+        <v>Alonso de Córdova 3000 - 4500</v>
       </c>
       <c r="E4" s="4">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="F4" s="5">
         <v>35</v>
       </c>
       <c r="G4" s="1">
-        <v>1036875</v>
+        <v>1106000</v>
       </c>
       <c r="H4" s="1">
-        <v>180000</v>
+        <v>200000</v>
       </c>
       <c r="I4" s="1">
-        <v>75000</v>
+        <v>90000</v>
       </c>
       <c r="J4" s="1">
-        <v>2141875</v>
+        <v>2246000</v>
       </c>
       <c r="K4" s="5">
-        <v>35000</v>
+        <v>22000</v>
       </c>
       <c r="L4" s="5">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="M4" s="1">
-        <v>3650000</v>
+        <v>4520000</v>
       </c>
       <c r="N4" s="5">
-        <v>220</v>
+        <v>850</v>
       </c>
       <c r="O4" s="1">
-        <v>3800</v>
+        <v>4200</v>
       </c>
       <c r="P4" s="1">
-        <v>1550</v>
+        <v>1650</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.5921052631578947</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="R4" s="5">
-        <v>158</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5">
@@ -2213,55 +2213,55 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Santiago Centro · Ahumada</v>
+        <v>Ñuñoa · Plaza Ñuñoa</v>
       </c>
       <c r="C5" t="str">
-        <v>Santiago</v>
+        <v>Ñuñoa</v>
       </c>
       <c r="D5" t="str">
-        <v>Paseo Ahumada / Estado</v>
+        <v>Av. Irarrázaval 2700 - 3200</v>
       </c>
       <c r="E5" s="4">
-        <v>0.55</v>
+        <v>0.48</v>
       </c>
       <c r="F5" s="5">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G5" s="1">
-        <v>651750</v>
+        <v>663600</v>
       </c>
       <c r="H5" s="1">
-        <v>140000</v>
+        <v>110000</v>
       </c>
       <c r="I5" s="1">
-        <v>55000</v>
+        <v>50000</v>
       </c>
       <c r="J5" s="1">
-        <v>1696750</v>
+        <v>1673600</v>
       </c>
       <c r="K5" s="5">
-        <v>95000</v>
+        <v>24000</v>
       </c>
       <c r="L5" s="5">
-        <v>145</v>
+        <v>48</v>
       </c>
       <c r="M5" s="1">
-        <v>1380000</v>
+        <v>1990000</v>
       </c>
       <c r="N5" s="5">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="O5" s="1">
-        <v>2900</v>
+        <v>3300</v>
       </c>
       <c r="P5" s="1">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.5344827586206896</v>
+        <v>0.5757575757575758</v>
       </c>
       <c r="R5" s="5">
-        <v>209</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6">
@@ -2269,55 +2269,55 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Vitacura · Alonso de Córdova</v>
+        <v>Apoquindo / El Bosque · Las Condes</v>
       </c>
       <c r="C6" t="str">
-        <v>Vitacura</v>
+        <v>Las Condes</v>
       </c>
       <c r="D6" t="str">
-        <v>Alonso de Córdova 3000 - 4500</v>
+        <v>Apoquindo 4000 - 4900</v>
       </c>
       <c r="E6" s="4">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="F6" s="5">
         <v>35</v>
       </c>
       <c r="G6" s="1">
-        <v>1106000</v>
+        <v>1036875</v>
       </c>
       <c r="H6" s="1">
-        <v>200000</v>
+        <v>180000</v>
       </c>
       <c r="I6" s="1">
-        <v>90000</v>
+        <v>75000</v>
       </c>
       <c r="J6" s="1">
-        <v>2246000</v>
+        <v>2141875</v>
       </c>
       <c r="K6" s="5">
-        <v>22000</v>
+        <v>35000</v>
       </c>
       <c r="L6" s="5">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="M6" s="1">
-        <v>4520000</v>
+        <v>3650000</v>
       </c>
       <c r="N6" s="5">
-        <v>850</v>
+        <v>220</v>
       </c>
       <c r="O6" s="1">
-        <v>4200</v>
+        <v>3800</v>
       </c>
       <c r="P6" s="1">
-        <v>1650</v>
+        <v>1550</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.6071428571428571</v>
+        <v>0.5921052631578947</v>
       </c>
       <c r="R6" s="5">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7">
@@ -2325,55 +2325,55 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Ñuñoa · Plaza Ñuñoa</v>
+        <v>Estación Central · USACH</v>
       </c>
       <c r="C7" t="str">
-        <v>Ñuñoa</v>
+        <v>Estación Central</v>
       </c>
       <c r="D7" t="str">
-        <v>Av. Irarrázaval 2700 - 3200</v>
+        <v>Av. Bdo OHiggins 3300 - 3700</v>
       </c>
       <c r="E7" s="4">
-        <v>0.48</v>
+        <v>0.38</v>
       </c>
       <c r="F7" s="5">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G7" s="1">
-        <v>663600</v>
+        <v>450300</v>
       </c>
       <c r="H7" s="1">
-        <v>110000</v>
+        <v>80000</v>
       </c>
       <c r="I7" s="1">
-        <v>50000</v>
+        <v>35000</v>
       </c>
       <c r="J7" s="1">
-        <v>1673600</v>
+        <v>1415300</v>
       </c>
       <c r="K7" s="5">
-        <v>24000</v>
+        <v>42000</v>
       </c>
       <c r="L7" s="5">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="M7" s="1">
-        <v>1990000</v>
+        <v>1050000</v>
       </c>
       <c r="N7" s="5">
-        <v>320</v>
+        <v>150</v>
       </c>
       <c r="O7" s="1">
-        <v>3300</v>
+        <v>2700</v>
       </c>
       <c r="P7" s="1">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.5757575757575758</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="R7" s="5">
-        <v>139</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8">
@@ -2381,55 +2381,55 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Estación Central · USACH</v>
+        <v>Santiago Centro · Ahumada</v>
       </c>
       <c r="C8" t="str">
-        <v>Estación Central</v>
+        <v>Santiago</v>
       </c>
       <c r="D8" t="str">
-        <v>Av. Bdo OHiggins 3300 - 3700</v>
+        <v>Paseo Ahumada / Estado</v>
       </c>
       <c r="E8" s="4">
-        <v>0.38</v>
+        <v>0.55</v>
       </c>
       <c r="F8" s="5">
         <v>30</v>
       </c>
       <c r="G8" s="1">
-        <v>450300</v>
+        <v>651750</v>
       </c>
       <c r="H8" s="1">
-        <v>80000</v>
+        <v>140000</v>
       </c>
       <c r="I8" s="1">
-        <v>35000</v>
+        <v>55000</v>
       </c>
       <c r="J8" s="1">
-        <v>1415300</v>
+        <v>1696750</v>
       </c>
       <c r="K8" s="5">
-        <v>42000</v>
+        <v>95000</v>
       </c>
       <c r="L8" s="5">
-        <v>32</v>
+        <v>145</v>
       </c>
       <c r="M8" s="1">
-        <v>1050000</v>
+        <v>1380000</v>
       </c>
       <c r="N8" s="5">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="O8" s="1">
-        <v>2700</v>
+        <v>2900</v>
       </c>
       <c r="P8" s="1">
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.5185185185185185</v>
+        <v>0.5344827586206896</v>
       </c>
       <c r="R8" s="5">
-        <v>147</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -2464,19 +2464,19 @@
         <v>Providencia</v>
       </c>
       <c r="D1" t="str">
+        <v>Vitacura</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Ñuñoa</v>
+      </c>
+      <c r="F1" t="str">
         <v>Apoquindo / El Bosque</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
+        <v>Estación Central</v>
+      </c>
+      <c r="H1" t="str">
         <v>Santiago Centro</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Vitacura</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Ñuñoa</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Estación Central</v>
       </c>
     </row>
     <row r="2">
@@ -2490,19 +2490,19 @@
         <v>0.65</v>
       </c>
       <c r="D2" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0.48</v>
+      </c>
+      <c r="F2" s="4">
         <v>0.75</v>
       </c>
-      <c r="E2" s="4">
+      <c r="G2" s="4">
+        <v>0.38</v>
+      </c>
+      <c r="H2" s="4">
         <v>0.55</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0.48</v>
-      </c>
-      <c r="H2" s="4">
-        <v>0.38</v>
       </c>
     </row>
     <row r="3">
@@ -2516,19 +2516,19 @@
         <v>898625</v>
       </c>
       <c r="D3" s="1">
+        <v>1106000</v>
+      </c>
+      <c r="E3" s="1">
+        <v>663600</v>
+      </c>
+      <c r="F3" s="1">
         <v>1036875</v>
       </c>
-      <c r="E3" s="1">
+      <c r="G3" s="1">
+        <v>450300</v>
+      </c>
+      <c r="H3" s="1">
         <v>651750</v>
-      </c>
-      <c r="F3" s="1">
-        <v>1106000</v>
-      </c>
-      <c r="G3" s="1">
-        <v>663600</v>
-      </c>
-      <c r="H3" s="1">
-        <v>450300</v>
       </c>
     </row>
     <row r="4">
@@ -2542,19 +2542,19 @@
         <v>150000</v>
       </c>
       <c r="D4" s="1">
+        <v>200000</v>
+      </c>
+      <c r="E4" s="1">
+        <v>110000</v>
+      </c>
+      <c r="F4" s="1">
         <v>180000</v>
       </c>
-      <c r="E4" s="1">
+      <c r="G4" s="1">
+        <v>80000</v>
+      </c>
+      <c r="H4" s="1">
         <v>140000</v>
-      </c>
-      <c r="F4" s="1">
-        <v>200000</v>
-      </c>
-      <c r="G4" s="1">
-        <v>110000</v>
-      </c>
-      <c r="H4" s="1">
-        <v>80000</v>
       </c>
     </row>
     <row r="5">
@@ -2568,19 +2568,19 @@
         <v>65000</v>
       </c>
       <c r="D5" s="1">
+        <v>90000</v>
+      </c>
+      <c r="E5" s="1">
+        <v>50000</v>
+      </c>
+      <c r="F5" s="1">
         <v>75000</v>
       </c>
-      <c r="E5" s="1">
+      <c r="G5" s="1">
+        <v>35000</v>
+      </c>
+      <c r="H5" s="1">
         <v>55000</v>
-      </c>
-      <c r="F5" s="1">
-        <v>90000</v>
-      </c>
-      <c r="G5" s="1">
-        <v>50000</v>
-      </c>
-      <c r="H5" s="1">
-        <v>35000</v>
       </c>
     </row>
     <row r="6">
@@ -2724,19 +2724,19 @@
         <v>1963625</v>
       </c>
       <c r="D11" s="1">
+        <v>2246000</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1673600</v>
+      </c>
+      <c r="F11" s="1">
         <v>2141875</v>
       </c>
-      <c r="E11" s="1">
+      <c r="G11" s="1">
+        <v>1415300</v>
+      </c>
+      <c r="H11" s="1">
         <v>1696750</v>
-      </c>
-      <c r="F11" s="1">
-        <v>2246000</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1673600</v>
-      </c>
-      <c r="H11" s="1">
-        <v>1415300</v>
       </c>
     </row>
     <row r="13">
@@ -2776,19 +2776,19 @@
         <v>4906072</v>
       </c>
       <c r="D15" s="1">
+        <v>5188447</v>
+      </c>
+      <c r="E15" s="1">
+        <v>4616047</v>
+      </c>
+      <c r="F15" s="1">
         <v>5084322</v>
       </c>
-      <c r="E15" s="1">
+      <c r="G15" s="1">
+        <v>4357747</v>
+      </c>
+      <c r="H15" s="1">
         <v>4639197</v>
-      </c>
-      <c r="F15" s="1">
-        <v>5188447</v>
-      </c>
-      <c r="G15" s="1">
-        <v>4616047</v>
-      </c>
-      <c r="H15" s="1">
-        <v>4357747</v>
       </c>
     </row>
     <row r="16">
@@ -2802,19 +2802,19 @@
         <v>58872864</v>
       </c>
       <c r="D16" s="1">
+        <v>62261364</v>
+      </c>
+      <c r="E16" s="1">
+        <v>55392564</v>
+      </c>
+      <c r="F16" s="1">
         <v>61011864</v>
       </c>
-      <c r="E16" s="1">
+      <c r="G16" s="1">
+        <v>52292964</v>
+      </c>
+      <c r="H16" s="1">
         <v>55670364</v>
-      </c>
-      <c r="F16" s="1">
-        <v>62261364</v>
-      </c>
-      <c r="G16" s="1">
-        <v>55392564</v>
-      </c>
-      <c r="H16" s="1">
-        <v>52292964</v>
       </c>
     </row>
     <row r="18">
@@ -2828,19 +2828,19 @@
         <v>1500</v>
       </c>
       <c r="D18" s="1">
+        <v>1650</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1400</v>
+      </c>
+      <c r="F18" s="1">
         <v>1550</v>
       </c>
-      <c r="E18" s="1">
+      <c r="G18" s="1">
+        <v>1300</v>
+      </c>
+      <c r="H18" s="1">
         <v>1350</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1650</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1400</v>
-      </c>
-      <c r="H18" s="1">
-        <v>1300</v>
       </c>
     </row>
     <row r="19">
@@ -2848,25 +2848,25 @@
         <v>Ingresos anuales caso base</v>
       </c>
       <c r="B19" s="1">
-        <v>216216000</v>
+        <v>189540000</v>
       </c>
       <c r="C19" s="1">
-        <v>210100800</v>
+        <v>154689600</v>
       </c>
       <c r="D19" s="1">
-        <v>187324800</v>
+        <v>155937600</v>
       </c>
       <c r="E19" s="1">
-        <v>189103200</v>
+        <v>143114400</v>
       </c>
       <c r="F19" s="1">
-        <v>158558400</v>
+        <v>149385600</v>
       </c>
       <c r="G19" s="1">
-        <v>143114400</v>
+        <v>123832800</v>
       </c>
       <c r="H19" s="1">
-        <v>123832800</v>
+        <v>111290400</v>
       </c>
     </row>
     <row r="20">
@@ -2874,25 +2874,25 @@
         <v>Costos variables anuales caso base</v>
       </c>
       <c r="B20" s="1">
-        <v>81681600</v>
+        <v>71604000</v>
       </c>
       <c r="C20" s="1">
-        <v>85176000</v>
+        <v>62712000</v>
       </c>
       <c r="D20" s="1">
-        <v>76408800</v>
+        <v>61261200</v>
       </c>
       <c r="E20" s="1">
-        <v>88030800</v>
+        <v>60715200</v>
       </c>
       <c r="F20" s="1">
-        <v>62290800</v>
+        <v>60933600</v>
       </c>
       <c r="G20" s="1">
-        <v>60715200</v>
+        <v>59623200</v>
       </c>
       <c r="H20" s="1">
-        <v>59623200</v>
+        <v>51807600</v>
       </c>
     </row>
     <row r="21">
@@ -2900,25 +2900,25 @@
         <v>Comisión tarjetas (2.8%)</v>
       </c>
       <c r="B21" s="1">
-        <v>6054048</v>
+        <v>5307120</v>
       </c>
       <c r="C21" s="1">
-        <v>5882822.4</v>
+        <v>4331308.8</v>
       </c>
       <c r="D21" s="1">
-        <v>5245094.4</v>
+        <v>4366252.8</v>
       </c>
       <c r="E21" s="1">
-        <v>5294889.600000001</v>
+        <v>4007203.2</v>
       </c>
       <c r="F21" s="1">
-        <v>4439635.2</v>
+        <v>4182796.8000000003</v>
       </c>
       <c r="G21" s="1">
-        <v>4007203.2</v>
+        <v>3467318.4</v>
       </c>
       <c r="H21" s="1">
-        <v>3467318.4</v>
+        <v>3116131.2</v>
       </c>
     </row>
     <row r="22">
@@ -2932,19 +2932,19 @@
         <v>2200</v>
       </c>
       <c r="D22" s="1">
+        <v>2550</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1900</v>
+      </c>
+      <c r="F22" s="1">
         <v>2250</v>
       </c>
-      <c r="E22" s="1">
+      <c r="G22" s="1">
+        <v>1400</v>
+      </c>
+      <c r="H22" s="1">
         <v>1550</v>
-      </c>
-      <c r="F22" s="1">
-        <v>2550</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1900</v>
-      </c>
-      <c r="H22" s="1">
-        <v>1400</v>
       </c>
     </row>
     <row r="23">
@@ -2958,19 +2958,19 @@
         <v>0.5945945945945946</v>
       </c>
       <c r="D23" s="2">
+        <v>0.6071428571428571</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="F23" s="2">
         <v>0.5921052631578947</v>
       </c>
-      <c r="E23" s="2">
+      <c r="G23" s="2">
+        <v>0.5185185185185185</v>
+      </c>
+      <c r="H23" s="2">
         <v>0.5344827586206896</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0.6071428571428571</v>
-      </c>
-      <c r="G23" s="2">
-        <v>0.5757575757575758</v>
-      </c>
-      <c r="H23" s="2">
-        <v>0.5185185185185185</v>
       </c>
     </row>
     <row r="24">
@@ -2978,25 +2978,25 @@
         <v>EBITDA año 1</v>
       </c>
       <c r="B24" s="1">
-        <v>5614332</v>
+        <v>-3103977</v>
       </c>
       <c r="C24" s="1">
-        <v>6600226</v>
+        <v>-10667401</v>
       </c>
       <c r="D24" s="1">
-        <v>-2892863</v>
+        <v>-12590780</v>
       </c>
       <c r="E24" s="1">
-        <v>-2992731</v>
+        <v>-12276963</v>
       </c>
       <c r="F24" s="1">
-        <v>-11755981</v>
+        <v>-14663800</v>
       </c>
       <c r="G24" s="1">
-        <v>-12276963</v>
+        <v>-18884706</v>
       </c>
       <c r="H24" s="1">
-        <v>-18884706</v>
+        <v>-24668694</v>
       </c>
     </row>
   </sheetData>
@@ -3718,34 +3718,34 @@
         <v>Las Condes</v>
       </c>
       <c r="D2">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="E2" s="1">
-        <v>51069054</v>
+        <v>48969554</v>
       </c>
       <c r="F2" s="1">
-        <v>5614332</v>
+        <v>-3103977</v>
       </c>
       <c r="G2" s="1">
-        <v>161650312</v>
+        <v>107168913</v>
       </c>
       <c r="H2" s="1">
-        <v>8545615</v>
+        <v>-33864960</v>
       </c>
       <c r="I2" s="1">
-        <v>298901997</v>
+        <v>227416744</v>
       </c>
       <c r="J2" s="2">
-        <v>0.6245770437265755</v>
+        <v>0.48968545245506934</v>
       </c>
       <c r="K2">
-        <v>2.57</v>
+        <v>3.21</v>
       </c>
       <c r="L2">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M2" t="str">
-        <v>Recomendado</v>
+        <v>Aceptable con riesgo</v>
       </c>
     </row>
     <row r="3">
@@ -3759,34 +3759,34 @@
         <v>Providencia</v>
       </c>
       <c r="D3">
-        <v>182</v>
+        <v>134</v>
       </c>
       <c r="E3" s="1">
-        <v>50510179</v>
+        <v>45830179</v>
       </c>
       <c r="F3" s="1">
-        <v>6600226</v>
+        <v>-10667401</v>
       </c>
       <c r="G3" s="1">
-        <v>154338627</v>
+        <v>46142432</v>
       </c>
       <c r="H3" s="1">
-        <v>9489071</v>
+        <v>-71656296</v>
       </c>
       <c r="I3" s="1">
-        <v>275421162</v>
+        <v>136400473</v>
       </c>
       <c r="J3" s="2">
-        <v>0.616604428708901</v>
+        <v>0.31500186806919506</v>
       </c>
       <c r="K3">
-        <v>2.58</v>
+        <v>4.07</v>
       </c>
       <c r="L3">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M3" t="str">
-        <v>Recomendado</v>
+        <v>Aceptable con riesgo</v>
       </c>
     </row>
     <row r="4">
@@ -3794,34 +3794,34 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Apoquindo / El Bosque · Las Condes</v>
+        <v>Vitacura · Alonso de Córdova</v>
       </c>
       <c r="C4" t="str">
-        <v>Las Condes</v>
+        <v>Vitacura</v>
       </c>
       <c r="D4">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="E4" s="1">
-        <v>49129304</v>
+        <v>46233867</v>
       </c>
       <c r="F4" s="1">
-        <v>-2892863</v>
+        <v>-12590780</v>
       </c>
       <c r="G4" s="1">
-        <v>98709622</v>
+        <v>41005310</v>
       </c>
       <c r="H4" s="1">
-        <v>-36138011</v>
+        <v>-79134298</v>
       </c>
       <c r="I4" s="1">
-        <v>201743858</v>
+        <v>135220831</v>
       </c>
       <c r="J4" s="2">
-        <v>0.4691992318618286</v>
+        <v>0.2940281915686557</v>
       </c>
       <c r="K4">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="L4">
         <v>65</v>
@@ -3835,34 +3835,34 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Santiago Centro · Ahumada</v>
+        <v>Ñuñoa · Plaza Ñuñoa</v>
       </c>
       <c r="C5" t="str">
-        <v>Santiago</v>
+        <v>Ñuñoa</v>
       </c>
       <c r="D5">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="E5" s="1">
-        <v>50437742</v>
+        <v>44689117</v>
       </c>
       <c r="F5" s="1">
-        <v>-2992731</v>
+        <v>-12276963</v>
       </c>
       <c r="G5" s="1">
-        <v>87093900</v>
+        <v>27541729</v>
       </c>
       <c r="H5" s="1">
-        <v>-39379309</v>
+        <v>-78151616</v>
       </c>
       <c r="I5" s="1">
-        <v>192412756</v>
+        <v>107294736</v>
       </c>
       <c r="J5" s="2">
-        <v>0.4328719148703745</v>
+        <v>0.25184266824949386</v>
       </c>
       <c r="K5">
-        <v>3.51</v>
+        <v>4.18</v>
       </c>
       <c r="L5">
         <v>65</v>
@@ -3876,34 +3876,34 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Vitacura · Alonso de Córdova</v>
+        <v>Apoquindo / El Bosque · Las Condes</v>
       </c>
       <c r="C6" t="str">
-        <v>Vitacura</v>
+        <v>Las Condes</v>
       </c>
       <c r="D6">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E6" s="1">
-        <v>46448367</v>
+        <v>45905304</v>
       </c>
       <c r="F6" s="1">
-        <v>-11755981</v>
+        <v>-14663800</v>
       </c>
       <c r="G6" s="1">
-        <v>46270049</v>
+        <v>24702079</v>
       </c>
       <c r="H6" s="1">
-        <v>-76006860</v>
+        <v>-93953528</v>
       </c>
       <c r="I6" s="1">
-        <v>143017713</v>
+        <v>110191079</v>
       </c>
       <c r="J6" s="2">
-        <v>0.3117614263631726</v>
+        <v>0.23635952735995852</v>
       </c>
       <c r="K6">
-        <v>4.07</v>
+        <v>4.21</v>
       </c>
       <c r="L6">
         <v>65</v>
@@ -3917,40 +3917,40 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Ñuñoa · Plaza Ñuñoa</v>
+        <v>Estación Central · USACH</v>
       </c>
       <c r="C7" t="str">
-        <v>Ñuñoa</v>
+        <v>Estación Central</v>
       </c>
       <c r="D7">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E7" s="1">
-        <v>44689117</v>
+        <v>43815867</v>
       </c>
       <c r="F7" s="1">
-        <v>-12276963</v>
+        <v>-18884706</v>
       </c>
       <c r="G7" s="1">
-        <v>27541729</v>
+        <v>-23503844</v>
       </c>
       <c r="H7" s="1">
-        <v>-78151616</v>
+        <v>-108796299</v>
       </c>
       <c r="I7" s="1">
-        <v>107294736</v>
+        <v>45745411</v>
       </c>
       <c r="J7" s="2">
-        <v>0.25184266824949386</v>
+        <v>0.030230875745438653</v>
       </c>
       <c r="K7">
-        <v>4.18</v>
+        <v>4.86</v>
       </c>
       <c r="L7">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="M7" t="str">
-        <v>Aceptable con riesgo</v>
+        <v>No conviene</v>
       </c>
     </row>
     <row r="8">
@@ -3958,37 +3958,34 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Estación Central · USACH</v>
+        <v>Santiago Centro · Ahumada</v>
       </c>
       <c r="C8" t="str">
-        <v>Estación Central</v>
+        <v>Santiago</v>
       </c>
       <c r="D8">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="E8" s="1">
-        <v>43815867</v>
+        <v>42891242</v>
       </c>
       <c r="F8" s="1">
-        <v>-18884706</v>
+        <v>-24668694</v>
       </c>
       <c r="G8" s="1">
-        <v>-23503844</v>
+        <v>-58283217</v>
       </c>
       <c r="H8" s="1">
-        <v>-108796299</v>
+        <v>-143350803</v>
       </c>
       <c r="I8" s="1">
-        <v>45745411</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0.030230875745438653</v>
-      </c>
-      <c r="K8">
-        <v>4.86</v>
+        <v>12292333</v>
+      </c>
+      <c r="K8" t="str">
+        <v>&gt; 5</v>
       </c>
       <c r="L8">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M8" t="str">
         <v>No conviene</v>
@@ -4021,7 +4018,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>VAN 161.650.312  ·  TIR 62.5%  ·  Payback 2.57 años</v>
+        <v>VAN 107.168.913  ·  TIR 49.0%  ·  Payback 3.21 años</v>
       </c>
     </row>
     <row r="4">
@@ -4055,19 +4052,19 @@
         <v/>
       </c>
       <c r="C5" s="5">
-        <v>26426</v>
+        <v>23166</v>
       </c>
       <c r="D5" s="5">
-        <v>36036</v>
+        <v>31590</v>
       </c>
       <c r="E5" s="5">
-        <v>43243</v>
+        <v>37908</v>
       </c>
       <c r="F5" s="5">
-        <v>48048</v>
+        <v>42120</v>
       </c>
       <c r="G5" s="5">
-        <v>49249</v>
+        <v>43173</v>
       </c>
     </row>
     <row r="6">
@@ -4078,19 +4075,19 @@
         <v/>
       </c>
       <c r="C6" s="1">
-        <v>118918800</v>
+        <v>104247000.00000001</v>
       </c>
       <c r="D6" s="1">
-        <v>162162000</v>
+        <v>142155000</v>
       </c>
       <c r="E6" s="1">
-        <v>194594400.00000003</v>
+        <v>170586000</v>
       </c>
       <c r="F6" s="1">
-        <v>216216000</v>
+        <v>189540000</v>
       </c>
       <c r="G6" s="1">
-        <v>221621400</v>
+        <v>194278499.99999997</v>
       </c>
     </row>
     <row r="7">
@@ -4101,19 +4098,19 @@
         <v/>
       </c>
       <c r="C7" s="1">
-        <v>-44924880</v>
+        <v>-39382200.00000001</v>
       </c>
       <c r="D7" s="1">
-        <v>-61261200</v>
+        <v>-53703000</v>
       </c>
       <c r="E7" s="1">
-        <v>-73513440</v>
+        <v>-64443600</v>
       </c>
       <c r="F7" s="1">
-        <v>-81681600</v>
+        <v>-71604000</v>
       </c>
       <c r="G7" s="1">
-        <v>-83723640</v>
+        <v>-73394099.99999999</v>
       </c>
     </row>
     <row r="8">
@@ -4147,19 +4144,19 @@
         <v/>
       </c>
       <c r="C9" s="1">
-        <v>-3329726.4</v>
+        <v>-2918916.0000000005</v>
       </c>
       <c r="D9" s="1">
-        <v>-4540536</v>
+        <v>-3980340</v>
       </c>
       <c r="E9" s="1">
-        <v>-5448643.200000001</v>
+        <v>-4776408</v>
       </c>
       <c r="F9" s="1">
-        <v>-6054048</v>
+        <v>-5307120</v>
       </c>
       <c r="G9" s="1">
-        <v>-6205399.2</v>
+        <v>-5439797.999999999</v>
       </c>
     </row>
     <row r="10">
@@ -4170,19 +4167,19 @@
         <v/>
       </c>
       <c r="C10" s="1">
-        <v>5614332.2447999995</v>
+        <v>-3103977.355199993</v>
       </c>
       <c r="D10" s="1">
-        <v>31310402.6448</v>
+        <v>19421798.6448</v>
       </c>
       <c r="E10" s="1">
-        <v>50582455.44480003</v>
+        <v>36316130.6448</v>
       </c>
       <c r="F10" s="1">
-        <v>63430490.64480001</v>
+        <v>47579018.6448</v>
       </c>
       <c r="G10" s="1">
-        <v>66642499.444800004</v>
+        <v>50394740.644799985</v>
       </c>
     </row>
     <row r="11">
@@ -4216,19 +4213,19 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>3051832.2447999995</v>
+        <v>-5666477.355199993</v>
       </c>
       <c r="D12" s="1">
-        <v>28747902.6448</v>
+        <v>16859298.6448</v>
       </c>
       <c r="E12" s="1">
-        <v>48019955.44480003</v>
+        <v>33753630.6448</v>
       </c>
       <c r="F12" s="1">
-        <v>60867990.64480001</v>
+        <v>45016518.6448</v>
       </c>
       <c r="G12" s="1">
-        <v>64079999.444800004</v>
+        <v>47832240.644799985</v>
       </c>
     </row>
     <row r="13">
@@ -4239,19 +4236,19 @@
         <v/>
       </c>
       <c r="C13" s="1">
-        <v>-762958.0611999999</v>
+        <v>0</v>
       </c>
       <c r="D13" s="1">
-        <v>-7186975.6612</v>
+        <v>-2798205.322400002</v>
       </c>
       <c r="E13" s="1">
-        <v>-12004988.861200007</v>
+        <v>-8438407.6612</v>
       </c>
       <c r="F13" s="1">
-        <v>-15216997.661200002</v>
+        <v>-11254129.6612</v>
       </c>
       <c r="G13" s="1">
-        <v>-16019999.861200001</v>
+        <v>-11958060.161199996</v>
       </c>
     </row>
     <row r="14">
@@ -4262,19 +4259,19 @@
         <v/>
       </c>
       <c r="C14" s="1">
-        <v>2288874.1835999996</v>
+        <v>-5666477.355199993</v>
       </c>
       <c r="D14" s="1">
-        <v>21560926.983599998</v>
+        <v>14061093.322399998</v>
       </c>
       <c r="E14" s="1">
-        <v>36014966.58360002</v>
+        <v>25315222.983599998</v>
       </c>
       <c r="F14" s="1">
-        <v>45650992.983600006</v>
+        <v>33762388.9836</v>
       </c>
       <c r="G14" s="1">
-        <v>48059999.5836</v>
+        <v>35874180.48359999</v>
       </c>
     </row>
     <row r="15">
@@ -4308,19 +4305,19 @@
         <v/>
       </c>
       <c r="C16" s="1">
-        <v>4851374.183599999</v>
+        <v>-3103977.3551999927</v>
       </c>
       <c r="D16" s="1">
-        <v>24123426.983599998</v>
+        <v>16623593.322399998</v>
       </c>
       <c r="E16" s="1">
-        <v>38577466.58360002</v>
+        <v>27877722.983599998</v>
       </c>
       <c r="F16" s="1">
-        <v>48213492.983600006</v>
+        <v>36324888.9836</v>
       </c>
       <c r="G16" s="1">
-        <v>50622499.5836</v>
+        <v>38436680.48359999</v>
       </c>
     </row>
     <row r="17">
@@ -4343,7 +4340,7 @@
         <v/>
       </c>
       <c r="G17" s="1">
-        <v>30569054</v>
+        <v>28469554</v>
       </c>
     </row>
     <row r="18">
@@ -4389,7 +4386,7 @@
         <v/>
       </c>
       <c r="G19" s="1">
-        <v>174936561.0426</v>
+        <v>132286194.19259995</v>
       </c>
     </row>
     <row r="20">
@@ -4420,7 +4417,7 @@
         <v>(-) Capital de trabajo</v>
       </c>
       <c r="B21" s="1">
-        <v>-30569054</v>
+        <v>-28469554</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -4443,22 +4440,22 @@
         <v>FLUJO NETO DE CAJA</v>
       </c>
       <c r="B22" s="1">
-        <v>-51069054</v>
+        <v>-48969554</v>
       </c>
       <c r="C22" s="1">
-        <v>4851374.183599999</v>
+        <v>-3103977.3551999927</v>
       </c>
       <c r="D22" s="1">
-        <v>24123426.983599998</v>
+        <v>16623593.322399998</v>
       </c>
       <c r="E22" s="1">
-        <v>38577466.58360002</v>
+        <v>27877722.983599998</v>
       </c>
       <c r="F22" s="1">
-        <v>48213492.983600006</v>
+        <v>36324888.9836</v>
       </c>
       <c r="G22" s="1">
-        <v>260540614.62620002</v>
+        <v>203604928.67619994</v>
       </c>
     </row>
     <row r="24">
@@ -4471,7 +4468,7 @@
         <v>VAN</v>
       </c>
       <c r="B25" s="1">
-        <v>161650312</v>
+        <v>107168913</v>
       </c>
     </row>
     <row r="26">
@@ -4479,7 +4476,7 @@
         <v>TIR</v>
       </c>
       <c r="B26" s="2">
-        <v>0.6245770437265755</v>
+        <v>0.48968545245506934</v>
       </c>
     </row>
     <row r="27">
@@ -4487,7 +4484,7 @@
         <v>Payback (años)</v>
       </c>
       <c r="B27">
-        <v>2.572724307463795</v>
+        <v>3.2084580369294096</v>
       </c>
     </row>
     <row r="28">
@@ -4540,7 +4537,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>VAN base: $161.650.312</v>
+        <v>VAN base: $107.168.913</v>
       </c>
     </row>
     <row r="4">
@@ -4568,19 +4565,19 @@
         <v>Ticket promedio</v>
       </c>
       <c r="B5" s="1">
-        <v>13571996</v>
+        <v>-26454560</v>
       </c>
       <c r="C5" s="1">
-        <v>88053151</v>
+        <v>42278490</v>
       </c>
       <c r="D5" s="1">
-        <v>161650312</v>
+        <v>107168913</v>
       </c>
       <c r="E5" s="1">
-        <v>235018365</v>
+        <v>171637670</v>
       </c>
       <c r="F5" s="1">
-        <v>308386418</v>
+        <v>235953820</v>
       </c>
     </row>
     <row r="6">
@@ -4588,19 +4585,19 @@
         <v>Demanda (combos/día)</v>
       </c>
       <c r="B6" s="1">
-        <v>73244133</v>
+        <v>29108271</v>
       </c>
       <c r="C6" s="1">
-        <v>117507277</v>
+        <v>68318570</v>
       </c>
       <c r="D6" s="1">
-        <v>161650312</v>
+        <v>107168913</v>
       </c>
       <c r="E6" s="1">
-        <v>205685227</v>
+        <v>145923556</v>
       </c>
       <c r="F6" s="1">
-        <v>249720143</v>
+        <v>184525593</v>
       </c>
     </row>
     <row r="7">
@@ -4608,19 +4605,19 @@
         <v>Costo variable insumo</v>
       </c>
       <c r="B7" s="1">
-        <v>220316586</v>
+        <v>158749747</v>
       </c>
       <c r="C7" s="1">
-        <v>190983449</v>
+        <v>132989089</v>
       </c>
       <c r="D7" s="1">
-        <v>161650312</v>
+        <v>107168913</v>
       </c>
       <c r="E7" s="1">
-        <v>132278375</v>
+        <v>81348738</v>
       </c>
       <c r="F7" s="1">
-        <v>102824249</v>
+        <v>55353172</v>
       </c>
     </row>
     <row r="8">
@@ -4628,19 +4625,19 @@
         <v>Arriendo UF/m²</v>
       </c>
       <c r="B8" s="1">
-        <v>174379389</v>
+        <v>119982882</v>
       </c>
       <c r="C8" s="1">
-        <v>168014850</v>
+        <v>113575897</v>
       </c>
       <c r="D8" s="1">
-        <v>161650312</v>
+        <v>107168913</v>
       </c>
       <c r="E8" s="1">
-        <v>155285772</v>
+        <v>100761929</v>
       </c>
       <c r="F8" s="1">
-        <v>148918533</v>
+        <v>94354945</v>
       </c>
     </row>
     <row r="9">
@@ -4648,19 +4645,19 @@
         <v>Sueldos planilla</v>
       </c>
       <c r="B9" s="1">
-        <v>179833296</v>
+        <v>125351897</v>
       </c>
       <c r="C9" s="1">
-        <v>170741804</v>
+        <v>116260405</v>
       </c>
       <c r="D9" s="1">
-        <v>161650312</v>
+        <v>107168913</v>
       </c>
       <c r="E9" s="1">
-        <v>152558820</v>
+        <v>98077421</v>
       </c>
       <c r="F9" s="1">
-        <v>143467328</v>
+        <v>88985929</v>
       </c>
     </row>
     <row r="11">
@@ -4693,19 +4690,19 @@
         <v>Ticket promedio</v>
       </c>
       <c r="B13" s="1">
-        <v>-148078316</v>
+        <v>-133623473</v>
       </c>
       <c r="C13" s="1">
-        <v>-73597161</v>
+        <v>-64890423</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>73368053</v>
+        <v>64468757</v>
       </c>
       <c r="F13" s="1">
-        <v>146736106</v>
+        <v>128784907</v>
       </c>
     </row>
     <row r="14">
@@ -4713,19 +4710,19 @@
         <v>Demanda (combos/día)</v>
       </c>
       <c r="B14" s="1">
-        <v>-88406179</v>
+        <v>-78060642</v>
       </c>
       <c r="C14" s="1">
-        <v>-44143035</v>
+        <v>-38850343</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>44034915</v>
+        <v>38754643</v>
       </c>
       <c r="F14" s="1">
-        <v>88069831</v>
+        <v>77356680</v>
       </c>
     </row>
     <row r="15">
@@ -4733,19 +4730,19 @@
         <v>Costo variable insumo</v>
       </c>
       <c r="B15" s="1">
-        <v>58666274</v>
+        <v>51580834</v>
       </c>
       <c r="C15" s="1">
-        <v>29333137</v>
+        <v>25820176</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>-29371937</v>
+        <v>-25820175</v>
       </c>
       <c r="F15" s="1">
-        <v>-58826063</v>
+        <v>-51815741</v>
       </c>
     </row>
     <row r="16">
@@ -4773,19 +4770,19 @@
         <v>Arriendo UF/m²</v>
       </c>
       <c r="B17" s="1">
-        <v>12729077</v>
+        <v>12813969</v>
       </c>
       <c r="C17" s="1">
-        <v>6364538</v>
+        <v>6406984</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>-6364540</v>
+        <v>-6406984</v>
       </c>
       <c r="F17" s="1">
-        <v>-12731779</v>
+        <v>-12813968</v>
       </c>
     </row>
   </sheetData>

--- a/public/exports/Analisis_Cafe_Combo_RM.xlsx
+++ b/public/exports/Analisis_Cafe_Combo_RM.xlsx
@@ -610,84 +610,84 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>AUDITORÍA DEL MODELO PREVIO</v>
+        <v>PARÁMETROS CLAVE DEL MODELO</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Antes</v>
+        <v>Variable</v>
       </c>
       <c r="B31" t="str">
-        <v>Ahora</v>
+        <v>Valor</v>
       </c>
       <c r="C31" t="str">
-        <v>Justificación</v>
+        <v>Fundamento</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Costo variable $1.100</v>
+        <v>Costo variable por combo</v>
       </c>
       <c r="B32" t="str">
         <v>Variable por zona $1.300-$1.700</v>
       </c>
       <c r="C32" t="str">
-        <v>Combo café+envasado: insumos + empaques + descartables = 40-50% del ticket</v>
+        <v>Espresso + alimento envasado + empaques + descartables ≈ 40-50% del ticket</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Costos fijos $350k/mes</v>
+        <v>Costos fijos no laborales</v>
       </c>
       <c r="B33" t="str">
         <v>$850k/mes (sin arriendo)</v>
       </c>
       <c r="C33" t="str">
-        <v>Faltaban: marketing $200k, aseo+pest $100k, software+contador $150k, seguros+mantenciones $150k, servicios $250k</v>
+        <v>Marketing $200k + aseo/pest $100k + software/contador $150k + seguros/mantenciones $150k + servicios $250k</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Sin comisión tarjetas</v>
+        <v>Comisión tarjetas</v>
       </c>
       <c r="B34" t="str">
         <v>2.8% sobre ingresos</v>
       </c>
       <c r="C34" t="str">
-        <v>Transbank/Getnet ~3.5% × 80% pago electrónico</v>
+        <v>Transbank/Getnet ~3.5% sobre ~80% de pago electrónico observado</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>g demanda 5% anual</v>
+        <v>Crecimiento demanda</v>
       </c>
       <c r="B35" t="str">
-        <v>g demanda 2.5% anual</v>
+        <v>2.5% anual sectorial</v>
       </c>
       <c r="C35" t="str">
-        <v>Crecimiento sectorial cafetería sin re-inversión 2-3%</v>
+        <v>Procafé Chile reporta consumo creciente 4-6%; aplicamos rango bajo conservador</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>VT por Gordon Growth (×10.7)</v>
+        <v>Valor terminal</v>
       </c>
       <c r="B36" t="str">
-        <v>VT por múltiplo EBITDA (×3.5)</v>
+        <v>Múltiplo EBITDA 3.5x</v>
       </c>
       <c r="C36" t="str">
-        <v>Cafetería independiente NO opera a perpetuidad sin reposición de equipos</v>
+        <v>Rango M&amp;A retail food Chile 3-5x; tomamos extremo bajo</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Tcc 11.5%</v>
+        <v>Tasa de descuento (Tcc)</v>
       </c>
       <c r="B37" t="str">
-        <v>Tcc 14%</v>
+        <v>14%</v>
       </c>
       <c r="C37" t="str">
-        <v>Retail food riesgo MEDIO-ALTO en Chile (alta tasa fracaso 50%+ a 3 años)</v>
+        <v>CAPM: Rf 5.5% (BTU 10y) + β 1.3 × ERP 6.5% (Damodaran 2024)</v>
       </c>
     </row>
     <row r="39">
@@ -1420,12 +1420,12 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Tras corrección del modelo (costos fijos reales, comisión tarjetas, valor terminal por múltiplo EBITDA y</v>
+        <v>Bajo el modelo financiero aplicado (costos fijos a precio de mercado, comisión de tarjetas, valor terminal</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Tcc retail food de 14%), solo 1 de las 7 ubicaciones evaluadas ofrece VAN claramente positivo y resiliente.</v>
+        <v>por múltiplo EBITDA y Tcc 14% para retail food), solo 1 de las 7 ubicaciones evaluadas ofrece VAN claramente positivo y resiliente.</v>
       </c>
     </row>
     <row r="35">
